--- a/Figures and Tables/Tables/Table S2 - Comprehensive metrics evolved and ancestral.xlsx
+++ b/Figures and Tables/Tables/Table S2 - Comprehensive metrics evolved and ancestral.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsk\Desktop\FLU PAPER\Manuscript Text and Figures\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA9A7BA-B559-401C-BF28-D9E76251A955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A3F04E-F64D-4279-BBF6-CECCCA8A22C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="19008" windowHeight="10584" xr2:uid="{F16E6D08-5EED-47EB-93C9-A1D5AE063C97}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F16E6D08-5EED-47EB-93C9-A1D5AE063C97}"/>
   </bookViews>
   <sheets>
     <sheet name="All metrics except virulence" sheetId="2" r:id="rId1"/>
@@ -306,12 +306,6 @@
     <t>Copy Number</t>
   </si>
   <si>
-    <t>npoly</t>
-  </si>
-  <si>
-    <t>Nei_D</t>
-  </si>
-  <si>
     <t>geneDiv</t>
   </si>
   <si>
@@ -400,6 +394,12 @@
   </si>
   <si>
     <t>Specific.infectivity</t>
+  </si>
+  <si>
+    <t>N_variants</t>
+  </si>
+  <si>
+    <t>DivergencePerSite</t>
   </si>
 </sst>
 </file>
@@ -1288,8 +1288,9 @@
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -1347,517 +1348,893 @@
         <v>88</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" t="s">
         <v>120</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>9768</v>
+        <v>10312</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H2">
-        <v>2.5857109999999999</v>
+        <v>0.79092459999999998</v>
       </c>
       <c r="I2">
-        <v>234420</v>
+        <v>832092</v>
       </c>
       <c r="J2">
-        <v>3790000</v>
+        <v>304000000</v>
       </c>
       <c r="K2" s="5">
-        <v>6.1852242744063327E-2</v>
+        <v>2.7371447368421051E-3</v>
       </c>
       <c r="L2">
-        <v>56</v>
-      </c>
-      <c r="M2" s="3">
-        <v>3.59E-4</v>
+        <v>8.1804089601118595E-4</v>
+      </c>
+      <c r="M2">
+        <v>17</v>
       </c>
       <c r="N2" s="3">
-        <v>3.3579999999999998E-4</v>
+        <v>1.4789999999999999E-4</v>
+      </c>
+      <c r="O2">
+        <v>160</v>
+      </c>
+      <c r="P2">
+        <v>777.32500000000005</v>
+      </c>
+      <c r="Q2">
+        <v>510.5</v>
+      </c>
+      <c r="R2">
+        <v>2166.6</v>
+      </c>
+      <c r="S2">
+        <v>630.27561656008004</v>
+      </c>
+      <c r="T2">
+        <v>332.25</v>
+      </c>
+      <c r="U2">
+        <v>2437.5</v>
+      </c>
+      <c r="V2">
+        <v>21087.690188614299</v>
+      </c>
+      <c r="W2">
+        <v>4.5216181276756098</v>
+      </c>
+      <c r="X2">
+        <v>7.5487179487179507E-2</v>
+      </c>
+      <c r="Y2">
+        <v>4.7501763803877397</v>
+      </c>
+      <c r="Z2">
+        <v>0.875</v>
+      </c>
+      <c r="AA2">
+        <v>8</v>
+      </c>
+      <c r="AB2">
+        <v>2278</v>
+      </c>
+      <c r="AC2">
+        <v>0.93456410256410305</v>
+      </c>
+      <c r="AD2">
+        <v>1067</v>
+      </c>
+      <c r="AE2">
+        <v>1297</v>
+      </c>
+      <c r="AF2">
+        <v>57</v>
+      </c>
+      <c r="AG2">
+        <v>92</v>
+      </c>
+      <c r="AH2">
+        <v>0.451353637901861</v>
+      </c>
+      <c r="AI2">
+        <v>0.38255033557047002</v>
+      </c>
+      <c r="AJ2">
+        <v>17236.848245240501</v>
+      </c>
+      <c r="AK2">
+        <v>928.24394415713505</v>
+      </c>
+      <c r="AL2">
+        <v>14141.216336768901</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>9773</v>
+        <v>10220</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H3">
-        <v>4.1547580000000002</v>
+        <v>1.608193</v>
       </c>
       <c r="I3">
-        <v>1645965</v>
+        <v>8532</v>
       </c>
       <c r="J3">
-        <v>245000000</v>
+        <v>22900000</v>
       </c>
       <c r="K3" s="5">
-        <v>6.7182244897959183E-3</v>
+        <v>3.7257641921397382E-4</v>
       </c>
       <c r="L3">
-        <v>45</v>
-      </c>
-      <c r="M3" s="3">
-        <v>2.6499999999999999E-4</v>
+        <v>1.2142433657639101E-3</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
       </c>
       <c r="N3" s="3">
-        <v>3.1050000000000001E-4</v>
+        <v>1.771E-4</v>
       </c>
       <c r="O3">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="P3">
-        <v>634.48780487804902</v>
+        <v>901.65686274509801</v>
       </c>
       <c r="Q3">
-        <v>493</v>
+        <v>619</v>
       </c>
       <c r="R3">
-        <v>1000.6</v>
+        <v>2179.9</v>
       </c>
       <c r="S3">
-        <v>516.672730958035</v>
+        <v>728.66489187788295</v>
       </c>
       <c r="T3">
-        <v>311</v>
+        <v>521.25</v>
       </c>
       <c r="U3">
-        <v>2219.5</v>
+        <v>9271.5</v>
       </c>
       <c r="V3">
-        <v>42147.964832050202</v>
+        <v>37168.362349890303</v>
       </c>
       <c r="W3">
-        <v>4.1266366246850099</v>
+        <v>2.1924551044871698</v>
       </c>
       <c r="X3">
-        <v>0.14214913268754201</v>
+        <v>0.48028905786550202</v>
       </c>
       <c r="Y3">
-        <v>4.7558309260586</v>
+        <v>4.3972551067602801</v>
       </c>
       <c r="Z3">
-        <v>0.75609756097560998</v>
+        <v>0.78431372549019596</v>
       </c>
       <c r="AA3">
         <v>8</v>
       </c>
       <c r="AB3">
-        <v>1910.5</v>
+        <v>9082</v>
       </c>
       <c r="AC3">
-        <v>0.860779454832169</v>
+        <v>0.97956102033112202</v>
       </c>
       <c r="AD3">
-        <v>423.5</v>
+        <v>864</v>
       </c>
       <c r="AE3">
-        <v>1763.5</v>
+        <v>8305.5</v>
       </c>
       <c r="AF3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AG3">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="AH3">
-        <v>0.19364426154549599</v>
+        <v>9.4225421233436898E-2</v>
       </c>
       <c r="AI3">
-        <v>0.29661016949152502</v>
+        <v>0.344444444444444</v>
       </c>
       <c r="AJ3">
-        <v>8465.0085073472492</v>
+        <v>22710.150591551599</v>
       </c>
       <c r="AK3">
-        <v>1453.04047707975</v>
+        <v>449.13836915702802</v>
       </c>
       <c r="AL3">
-        <v>26219.701942101699</v>
+        <v>40825.3567611705</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>9783</v>
+        <v>10300</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4">
-        <v>3.7346490000000001</v>
+        <v>51</v>
       </c>
       <c r="I4">
-        <v>1459932</v>
+        <v>3220</v>
       </c>
       <c r="J4">
-        <v>12100000</v>
+        <v>141000000</v>
       </c>
       <c r="K4" s="5">
-        <v>0.12065553719008265</v>
+        <v>2.2836879432624115E-5</v>
       </c>
       <c r="L4">
-        <v>40</v>
-      </c>
-      <c r="M4" s="3">
-        <v>2.6180000000000002E-4</v>
+        <v>1.19744537098911E-3</v>
+      </c>
+      <c r="M4">
+        <v>21</v>
       </c>
       <c r="N4" s="3">
-        <v>4.1889999999999999E-4</v>
+        <v>3.4499999999999998E-4</v>
+      </c>
+      <c r="O4">
+        <v>312</v>
+      </c>
+      <c r="P4">
+        <v>812.61538461538498</v>
+      </c>
+      <c r="Q4">
+        <v>499.5</v>
+      </c>
+      <c r="R4">
+        <v>2258.6</v>
+      </c>
+      <c r="S4">
+        <v>687.62624879088105</v>
+      </c>
+      <c r="T4">
+        <v>373.25</v>
+      </c>
+      <c r="U4">
+        <v>16339</v>
+      </c>
+      <c r="V4">
+        <v>59529.615620070297</v>
+      </c>
+      <c r="W4">
+        <v>4.4205838874190002</v>
+      </c>
+      <c r="X4">
+        <v>0.148540302344085</v>
+      </c>
+      <c r="Y4">
+        <v>5.3746788835116002</v>
+      </c>
+      <c r="Z4">
+        <v>0.91346153846153799</v>
+      </c>
+      <c r="AA4">
+        <v>8</v>
+      </c>
+      <c r="AB4">
+        <v>16139.5</v>
+      </c>
+      <c r="AC4">
+        <v>0.98778995042536299</v>
+      </c>
+      <c r="AD4">
+        <v>5844.5</v>
+      </c>
+      <c r="AE4">
+        <v>10335</v>
+      </c>
+      <c r="AF4">
+        <v>93</v>
+      </c>
+      <c r="AG4">
+        <v>208</v>
+      </c>
+      <c r="AH4">
+        <v>0.36122871534967099</v>
+      </c>
+      <c r="AI4">
+        <v>0.308970099667774</v>
+      </c>
+      <c r="AJ4">
+        <v>24910.7641359999</v>
+      </c>
+      <c r="AK4">
+        <v>1252.4706118874601</v>
+      </c>
+      <c r="AL4">
+        <v>65590.119639837299</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>9776</v>
+        <v>10009</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5">
-        <v>3.308271</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>192909</v>
+        <v>3220</v>
       </c>
       <c r="J5">
-        <v>1800000</v>
+        <v>73200000</v>
       </c>
       <c r="K5" s="5">
-        <v>0.10717166666666667</v>
+        <v>4.3989071038251367E-5</v>
       </c>
       <c r="L5">
-        <v>25</v>
-      </c>
-      <c r="M5" s="3">
-        <v>3.3280000000000001E-4</v>
+        <v>9.7708716676479204E-4</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
       </c>
       <c r="N5" s="3">
-        <v>1.8039999999999999E-4</v>
+        <v>5.4600000000000004E-4</v>
+      </c>
+      <c r="O5">
+        <v>65</v>
+      </c>
+      <c r="P5">
+        <v>722.323076923077</v>
+      </c>
+      <c r="Q5">
+        <v>521</v>
+      </c>
+      <c r="R5">
+        <v>1896</v>
+      </c>
+      <c r="S5">
+        <v>591.84286099891801</v>
+      </c>
+      <c r="T5">
+        <v>354</v>
+      </c>
+      <c r="U5">
+        <v>6412.5</v>
+      </c>
+      <c r="V5">
+        <v>37484.871534727099</v>
+      </c>
+      <c r="W5">
+        <v>2.00770191706984</v>
+      </c>
+      <c r="X5">
+        <v>0.53512670565302101</v>
+      </c>
+      <c r="Y5">
+        <v>4.1104044532285604</v>
+      </c>
+      <c r="Z5">
+        <v>0.67692307692307696</v>
+      </c>
+      <c r="AA5">
+        <v>8</v>
+      </c>
+      <c r="AB5">
+        <v>6236</v>
+      </c>
+      <c r="AC5">
+        <v>0.97247563352826505</v>
+      </c>
+      <c r="AD5">
+        <v>4065</v>
+      </c>
+      <c r="AE5">
+        <v>2287.5</v>
+      </c>
+      <c r="AF5">
+        <v>18</v>
+      </c>
+      <c r="AG5">
+        <v>40</v>
+      </c>
+      <c r="AH5">
+        <v>0.63990554899645802</v>
+      </c>
+      <c r="AI5">
+        <v>0.31034482758620702</v>
+      </c>
+      <c r="AJ5">
+        <v>21308.731721640401</v>
+      </c>
+      <c r="AK5">
+        <v>305.03927145503599</v>
+      </c>
+      <c r="AL5">
+        <v>30093.297357006399</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>9769</v>
+        <v>10309</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>3.085051</v>
+        <v>3.8831820000000001</v>
       </c>
       <c r="I6">
-        <v>3589146</v>
+        <v>17294</v>
       </c>
       <c r="J6">
-        <v>167000000</v>
+        <v>65200000</v>
       </c>
       <c r="K6" s="5">
-        <v>2.1491892215568863E-2</v>
+        <v>2.6524539877300615E-4</v>
       </c>
       <c r="L6">
-        <v>47</v>
-      </c>
-      <c r="M6" s="3">
-        <v>2.6899999999999998E-4</v>
+        <v>1.33616755931704E-3</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
       </c>
       <c r="N6" s="3">
-        <v>3.2699999999999998E-4</v>
+        <v>1.4760000000000001E-4</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="P6">
-        <v>760.01960784313701</v>
+        <v>713.71980676328496</v>
       </c>
       <c r="Q6">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="R6">
-        <v>2121</v>
+        <v>1254.5999999999999</v>
       </c>
       <c r="S6">
-        <v>590.22499066698504</v>
+        <v>561.92540770914502</v>
       </c>
       <c r="T6">
-        <v>359</v>
+        <v>336.5</v>
       </c>
       <c r="U6">
-        <v>2549.5</v>
+        <v>5393.5</v>
       </c>
       <c r="V6">
-        <v>51309.438057081701</v>
+        <v>38521.651821192201</v>
       </c>
       <c r="W6">
-        <v>2.1344300805563301</v>
+        <v>4.2872996119947899</v>
       </c>
       <c r="X6">
-        <v>0.43616395371641498</v>
+        <v>0.14378418466672799</v>
       </c>
       <c r="Y6">
-        <v>3.8774611479745298</v>
+        <v>5.1124706487555196</v>
       </c>
       <c r="Z6">
-        <v>0.70588235294117696</v>
+        <v>0.82608695652173902</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>2401.5</v>
+        <v>5096</v>
       </c>
       <c r="AC6">
-        <v>0.94194940184349896</v>
+        <v>0.944841012329656</v>
       </c>
       <c r="AD6">
-        <v>982.5</v>
+        <v>1757.5</v>
       </c>
       <c r="AE6">
-        <v>1530</v>
+        <v>3537</v>
       </c>
       <c r="AF6">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="AG6">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="AH6">
-        <v>0.39104477611940303</v>
+        <v>0.33194824818207602</v>
       </c>
       <c r="AI6">
-        <v>0.32608695652173902</v>
+        <v>0.335051546391753</v>
       </c>
       <c r="AJ6">
-        <v>6735.3550491107299</v>
+        <v>16626.0705569606</v>
       </c>
       <c r="AK6">
-        <v>757.19839010912403</v>
+        <v>1245.0326088225199</v>
       </c>
       <c r="AL6">
-        <v>37852.495991827702</v>
+        <v>32440.016307653499</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>9774</v>
+        <v>10299</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7">
-        <v>3.085051</v>
+        <v>49</v>
       </c>
       <c r="I7">
-        <v>621165</v>
-      </c>
-      <c r="K7" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>27200000</v>
+      </c>
+      <c r="K7" s="5">
+        <v>3.6764705882352938E-8</v>
+      </c>
+      <c r="L7">
+        <v>1.45336480085369E-3</v>
+      </c>
+      <c r="M7">
+        <v>24</v>
+      </c>
+      <c r="N7" s="3">
+        <v>2.0709999999999999E-4</v>
+      </c>
+      <c r="O7">
+        <v>150</v>
+      </c>
+      <c r="P7">
+        <v>813.72666666666703</v>
+      </c>
+      <c r="Q7">
+        <v>518.5</v>
+      </c>
+      <c r="R7">
+        <v>2166.4</v>
+      </c>
+      <c r="S7">
+        <v>700.55688200295401</v>
+      </c>
+      <c r="T7">
+        <v>454</v>
+      </c>
+      <c r="U7">
+        <v>3896.5</v>
+      </c>
+      <c r="V7">
+        <v>47278.002325241097</v>
+      </c>
+      <c r="W7">
+        <v>4.0397075671329299</v>
+      </c>
+      <c r="X7">
+        <v>0.114590016681637</v>
+      </c>
+      <c r="Y7">
+        <v>4.8685175370258396</v>
+      </c>
+      <c r="Z7">
+        <v>0.78666666666666696</v>
+      </c>
+      <c r="AA7">
+        <v>8</v>
+      </c>
+      <c r="AB7">
+        <v>3584</v>
+      </c>
+      <c r="AC7">
+        <v>0.91979982035159802</v>
+      </c>
+      <c r="AD7">
+        <v>1474</v>
+      </c>
+      <c r="AE7">
+        <v>2298.5</v>
+      </c>
+      <c r="AF7">
+        <v>59</v>
+      </c>
+      <c r="AG7">
+        <v>80</v>
+      </c>
+      <c r="AH7">
+        <v>0.39072233267064299</v>
+      </c>
+      <c r="AI7">
+        <v>0.42446043165467601</v>
+      </c>
+      <c r="AJ7">
+        <v>12504.7161306859</v>
+      </c>
+      <c r="AK7">
+        <v>1199.5474222074299</v>
+      </c>
+      <c r="AL7">
+        <v>31160.243537541799</v>
+      </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>9777</v>
+        <v>10307</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8">
-        <v>3.2389399999999999</v>
+        <v>59</v>
       </c>
       <c r="I8">
-        <v>882194</v>
-      </c>
-      <c r="K8" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>47900000</v>
+      </c>
+      <c r="K8" s="5">
+        <v>2.0876826722338206E-8</v>
+      </c>
+      <c r="L8">
+        <v>1.47669006660289E-3</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2.8640000000000002E-4</v>
+      </c>
+      <c r="O8">
+        <v>203</v>
+      </c>
+      <c r="P8">
+        <v>876.68965517241395</v>
+      </c>
+      <c r="Q8">
+        <v>604</v>
+      </c>
+      <c r="R8">
+        <v>2171.4</v>
+      </c>
+      <c r="S8">
+        <v>662.97163838907602</v>
+      </c>
+      <c r="T8">
+        <v>468.5</v>
+      </c>
+      <c r="U8">
+        <v>10231</v>
+      </c>
+      <c r="V8">
+        <v>55404.862127587898</v>
+      </c>
+      <c r="W8">
+        <v>3.8637220434180501</v>
+      </c>
+      <c r="X8">
+        <v>0.115091388916039</v>
+      </c>
+      <c r="Y8">
+        <v>5.1249997355283998</v>
+      </c>
+      <c r="Z8">
+        <v>0.79310344827586199</v>
+      </c>
+      <c r="AA8">
+        <v>8</v>
+      </c>
+      <c r="AB8">
+        <v>9821.5</v>
+      </c>
+      <c r="AC8">
+        <v>0.95997458703938998</v>
+      </c>
+      <c r="AD8">
+        <v>4159</v>
+      </c>
+      <c r="AE8">
+        <v>5989</v>
+      </c>
+      <c r="AF8">
+        <v>64</v>
+      </c>
+      <c r="AG8">
+        <v>128</v>
+      </c>
+      <c r="AH8">
+        <v>0.409834450137958</v>
+      </c>
+      <c r="AI8">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="AJ8">
+        <v>24710.039805949898</v>
+      </c>
+      <c r="AK8">
+        <v>821.528421622049</v>
+      </c>
+      <c r="AL8">
+        <v>41404.223062143799</v>
+      </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>9786</v>
+        <v>9776</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -1869,327 +2246,424 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9">
-        <v>3.2389399999999999</v>
+        <v>3.308271</v>
       </c>
       <c r="I9">
-        <v>2430557</v>
+        <v>192909</v>
       </c>
       <c r="J9">
-        <v>422000000</v>
+        <v>1800000</v>
       </c>
       <c r="K9" s="5">
-        <v>5.759613744075829E-3</v>
+        <v>0.10717166666666667</v>
       </c>
       <c r="L9">
-        <v>57</v>
-      </c>
-      <c r="M9" s="3">
-        <v>2.3460000000000001E-4</v>
+        <v>1.4413944551810399E-3</v>
+      </c>
+      <c r="M9">
+        <v>25</v>
       </c>
       <c r="N9" s="3">
-        <v>5.5690000000000004E-4</v>
-      </c>
-      <c r="O9">
-        <v>115</v>
-      </c>
-      <c r="P9">
-        <v>657.573913043478</v>
-      </c>
-      <c r="Q9">
-        <v>477</v>
-      </c>
-      <c r="R9">
-        <v>1180.2</v>
-      </c>
-      <c r="S9">
-        <v>496.67634031912502</v>
-      </c>
-      <c r="T9">
-        <v>331.5</v>
-      </c>
-      <c r="U9">
-        <v>1411</v>
-      </c>
-      <c r="V9">
-        <v>11727.8002217348</v>
-      </c>
-      <c r="W9">
-        <v>4.3738540755196498</v>
-      </c>
-      <c r="X9">
-        <v>7.3352232459248795E-2</v>
-      </c>
-      <c r="Y9">
-        <v>4.6439442759047802</v>
-      </c>
-      <c r="Z9">
-        <v>0.75652173913043497</v>
-      </c>
-      <c r="AA9">
-        <v>8</v>
-      </c>
-      <c r="AB9">
-        <v>1169.5</v>
-      </c>
-      <c r="AC9">
-        <v>0.82884479092842001</v>
-      </c>
-      <c r="AD9">
-        <v>381.5</v>
-      </c>
-      <c r="AE9">
-        <v>893</v>
-      </c>
-      <c r="AF9">
-        <v>35</v>
-      </c>
-      <c r="AG9">
-        <v>63</v>
-      </c>
-      <c r="AH9">
-        <v>0.29933307179286001</v>
-      </c>
-      <c r="AI9">
-        <v>0.35714285714285698</v>
-      </c>
-      <c r="AJ9">
-        <v>17483.652362722099</v>
-      </c>
-      <c r="AK9">
-        <v>657.75730158761303</v>
-      </c>
-      <c r="AL9">
-        <v>8070.39610904454</v>
+        <v>1.8039999999999999E-4</v>
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9770</v>
+        <v>10302</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10">
-        <v>4.5517370000000001</v>
+        <v>46</v>
       </c>
       <c r="I10">
-        <v>4700982</v>
+        <v>21534</v>
       </c>
       <c r="J10">
-        <v>668000000</v>
+        <v>12700000</v>
       </c>
       <c r="K10" s="5">
-        <v>7.0373982035928147E-3</v>
+        <v>1.6955905511811024E-3</v>
       </c>
       <c r="L10">
-        <v>38</v>
-      </c>
-      <c r="M10" s="3">
-        <v>3.2539999999999999E-4</v>
+        <v>1.81065053561966E-3</v>
+      </c>
+      <c r="M10">
+        <v>28</v>
       </c>
       <c r="N10" s="3">
-        <v>3.8559999999999999E-4</v>
+        <v>2.4659999999999998E-4</v>
+      </c>
+      <c r="O10">
+        <v>30</v>
+      </c>
+      <c r="P10">
+        <v>971.2</v>
+      </c>
+      <c r="Q10">
+        <v>742</v>
+      </c>
+      <c r="R10">
+        <v>2265</v>
+      </c>
+      <c r="S10">
+        <v>728.30234343181701</v>
+      </c>
+      <c r="T10">
+        <v>566.75</v>
+      </c>
+      <c r="U10">
+        <v>261.5</v>
+      </c>
+      <c r="V10">
+        <v>4840.6612511248704</v>
+      </c>
+      <c r="W10">
+        <v>3.2475259107184198</v>
+      </c>
+      <c r="X10">
+        <v>0.151051625239006</v>
+      </c>
+      <c r="Y10">
+        <v>3.4011973816621599</v>
+      </c>
+      <c r="Z10">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="AA10">
+        <v>7</v>
+      </c>
+      <c r="AB10">
+        <v>182</v>
+      </c>
+      <c r="AC10">
+        <v>0.695984703632887</v>
+      </c>
+      <c r="AD10">
+        <v>80.5</v>
+      </c>
+      <c r="AE10">
+        <v>133</v>
+      </c>
+      <c r="AF10">
+        <v>10</v>
+      </c>
+      <c r="AG10">
+        <v>14</v>
+      </c>
+      <c r="AH10">
+        <v>0.37704918032786899</v>
+      </c>
+      <c r="AI10">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="AJ10">
+        <v>6884.5760893734596</v>
+      </c>
+      <c r="AK10">
+        <v>435.75667710762701</v>
+      </c>
+      <c r="AL10">
+        <v>3798.3457021214799</v>
       </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>9775</v>
+        <v>10314</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H11">
-        <v>4.5517370000000001</v>
+        <v>1.029485</v>
       </c>
       <c r="I11">
-        <v>6440492</v>
-      </c>
-      <c r="K11" s="5"/>
+        <v>107504</v>
+      </c>
+      <c r="J11">
+        <v>193000000</v>
+      </c>
+      <c r="K11" s="5">
+        <v>5.5701554404145078E-4</v>
+      </c>
+      <c r="L11">
+        <v>1.8512918341183401E-3</v>
+      </c>
+      <c r="M11">
+        <v>28</v>
+      </c>
+      <c r="N11" s="3">
+        <v>2.1359999999999999E-4</v>
+      </c>
+      <c r="O11">
+        <v>130</v>
+      </c>
+      <c r="P11">
+        <v>815.96923076923099</v>
+      </c>
+      <c r="Q11">
+        <v>530.5</v>
+      </c>
+      <c r="R11">
+        <v>2172</v>
+      </c>
+      <c r="S11">
+        <v>697.30149784069499</v>
+      </c>
+      <c r="T11">
+        <v>431.75</v>
+      </c>
+      <c r="U11">
+        <v>7432.5</v>
+      </c>
+      <c r="V11">
+        <v>37974.828435506599</v>
+      </c>
+      <c r="W11">
+        <v>3.6964477493640602</v>
+      </c>
+      <c r="X11">
+        <v>9.2566431214261696E-2</v>
+      </c>
+      <c r="Y11">
+        <v>4.6608972119552599</v>
+      </c>
+      <c r="Z11">
+        <v>0.89230769230769202</v>
+      </c>
+      <c r="AA11">
+        <v>8</v>
+      </c>
+      <c r="AB11">
+        <v>7268.5</v>
+      </c>
+      <c r="AC11">
+        <v>0.97793474604776298</v>
+      </c>
+      <c r="AD11">
+        <v>3698</v>
+      </c>
+      <c r="AE11">
+        <v>3646</v>
+      </c>
+      <c r="AF11">
+        <v>50</v>
+      </c>
+      <c r="AG11">
+        <v>72</v>
+      </c>
+      <c r="AH11">
+        <v>0.50354030501089297</v>
+      </c>
+      <c r="AI11">
+        <v>0.409836065573771</v>
+      </c>
+      <c r="AJ11">
+        <v>25902.683211019201</v>
+      </c>
+      <c r="AK11">
+        <v>501.87850787866199</v>
+      </c>
+      <c r="AL11">
+        <v>28693.938536985799</v>
+      </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>9785</v>
+        <v>10317</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H12">
-        <v>4.5517370000000001</v>
+        <v>0.4624934</v>
       </c>
       <c r="I12">
-        <v>4654231</v>
+        <v>18605</v>
       </c>
       <c r="J12">
-        <v>650000000</v>
+        <v>47700000</v>
       </c>
       <c r="K12" s="5">
-        <v>7.1603553846153849E-3</v>
+        <v>3.9004192872117401E-4</v>
       </c>
       <c r="L12">
-        <v>38</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3.2430000000000002E-4</v>
+        <v>1.7904341946570501E-3</v>
+      </c>
+      <c r="M12">
+        <v>29</v>
       </c>
       <c r="N12" s="3">
-        <v>3.6870000000000002E-4</v>
+        <v>1.9110000000000001E-4</v>
       </c>
       <c r="O12">
-        <v>273</v>
+        <v>65</v>
       </c>
       <c r="P12">
-        <v>573.48351648351604</v>
+        <v>821.09230769230805</v>
       </c>
       <c r="Q12">
-        <v>449</v>
+        <v>706</v>
       </c>
       <c r="R12">
-        <v>796.8</v>
+        <v>1392.6</v>
       </c>
       <c r="S12">
-        <v>438.18480092771301</v>
+        <v>528.52946710297397</v>
       </c>
       <c r="T12">
-        <v>228</v>
+        <v>484</v>
       </c>
       <c r="U12">
-        <v>4849.5</v>
+        <v>560</v>
       </c>
       <c r="V12">
-        <v>45008.789331490698</v>
+        <v>11069.884594229899</v>
       </c>
       <c r="W12">
-        <v>4.7762124998591098</v>
+        <v>4.1115170819403</v>
       </c>
       <c r="X12">
-        <v>0.13640581503247801</v>
+        <v>3.5714285714285698E-2</v>
       </c>
       <c r="Y12">
-        <v>5.3336622087019396</v>
+        <v>4.1104044532285604</v>
       </c>
       <c r="Z12">
-        <v>0.86813186813186805</v>
+        <v>0.67692307692307696</v>
       </c>
       <c r="AA12">
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>4478.5</v>
+        <v>388</v>
       </c>
       <c r="AC12">
-        <v>0.92349726775956298</v>
+        <v>0.69285714285714295</v>
       </c>
       <c r="AD12">
-        <v>1660.5</v>
+        <v>160.5</v>
       </c>
       <c r="AE12">
-        <v>3130.5</v>
+        <v>300</v>
       </c>
       <c r="AF12">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="AG12">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="AH12">
-        <v>0.34658735128365697</v>
+        <v>0.34853420195439699</v>
       </c>
       <c r="AI12">
         <v>0.35849056603773599</v>
       </c>
       <c r="AJ12">
-        <v>15727.309826930201</v>
+        <v>6354.2388740367996</v>
       </c>
       <c r="AK12">
-        <v>1735.83405556453</v>
+        <v>1022.9391952132599</v>
       </c>
       <c r="AL12">
-        <v>30834.898360660001</v>
+        <v>8813.0146049142204</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>9790</v>
+        <v>9500</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H13">
-        <v>4.5517370000000001</v>
+        <v>1.5027079999999999</v>
       </c>
       <c r="I13">
-        <v>8627461</v>
-      </c>
-      <c r="K13" s="5"/>
+        <v>644049</v>
+      </c>
+      <c r="J13">
+        <v>135000000</v>
+      </c>
+      <c r="K13" s="5">
+        <v>4.7707333333333332E-3</v>
+      </c>
+      <c r="L13">
+        <v>1.7295644718869599E-3</v>
+      </c>
+      <c r="M13">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3">
+        <v>5.4469999999999996E-4</v>
+      </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -2208,7 +2682,7 @@
         <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
         <v>49</v>
@@ -2226,10 +2700,10 @@
         <v>3.2192339832869082E-3</v>
       </c>
       <c r="L14">
+        <v>1.6413312371945799E-3</v>
+      </c>
+      <c r="M14">
         <v>32</v>
-      </c>
-      <c r="M14" s="3">
-        <v>6.803E-4</v>
       </c>
       <c r="N14" s="3">
         <v>1.552E-4</v>
@@ -2309,7 +2783,7 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>9518</v>
+        <v>9537</v>
       </c>
       <c r="B15" t="s">
         <v>61</v>
@@ -2321,417 +2795,425 @@
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H15">
-        <v>0.62796320000000005</v>
+        <v>3.1063329999999998</v>
       </c>
       <c r="I15">
         <v>530001</v>
       </c>
       <c r="J15">
-        <v>16900000</v>
+        <v>315000000</v>
       </c>
       <c r="K15" s="5">
-        <v>3.1361005917159762E-2</v>
+        <v>1.6825428571428571E-3</v>
       </c>
       <c r="L15">
-        <v>69</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2.2690000000000001E-4</v>
+        <v>2.0184207045922898E-3</v>
+      </c>
+      <c r="M15">
+        <v>33</v>
       </c>
       <c r="N15" s="3">
-        <v>6.6560000000000002E-4</v>
-      </c>
-      <c r="O15">
-        <v>33</v>
-      </c>
-      <c r="P15">
-        <v>986.09090909090901</v>
-      </c>
-      <c r="Q15">
-        <v>592</v>
-      </c>
-      <c r="R15">
-        <v>2251.8000000000002</v>
-      </c>
-      <c r="S15">
-        <v>877.78034566016197</v>
-      </c>
-      <c r="T15">
-        <v>617</v>
-      </c>
-      <c r="U15">
-        <v>451</v>
-      </c>
-      <c r="V15">
-        <v>39694.298382773202</v>
-      </c>
-      <c r="W15">
-        <v>3.06689569803916</v>
-      </c>
-      <c r="X15">
-        <v>0.23725055432372499</v>
-      </c>
-      <c r="Y15">
-        <v>3.45449864143254</v>
-      </c>
-      <c r="Z15">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="AA15">
-        <v>8</v>
-      </c>
-      <c r="AB15">
-        <v>332.5</v>
-      </c>
-      <c r="AC15">
-        <v>0.73725055432372499</v>
-      </c>
-      <c r="AD15">
-        <v>77.5</v>
-      </c>
-      <c r="AE15">
-        <v>347.5</v>
-      </c>
-      <c r="AF15">
-        <v>8</v>
-      </c>
-      <c r="AG15">
-        <v>21</v>
-      </c>
-      <c r="AH15">
-        <v>0.182352941176471</v>
-      </c>
-      <c r="AI15">
-        <v>0.27586206896551702</v>
-      </c>
-      <c r="AJ15">
-        <v>2381.8632692490401</v>
-      </c>
-      <c r="AK15">
-        <v>1385.4699564851301</v>
-      </c>
-      <c r="AL15">
-        <v>18934.756071963398</v>
+        <v>3.703E-4</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>9500</v>
+        <v>10313</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H16">
-        <v>1.5027079999999999</v>
+        <v>3.7922910000000001</v>
       </c>
       <c r="I16">
-        <v>644049</v>
+        <v>59909</v>
       </c>
       <c r="J16">
-        <v>135000000</v>
+        <v>47700000</v>
       </c>
       <c r="K16" s="5">
-        <v>4.7707333333333332E-3</v>
+        <v>1.2559538784067087E-3</v>
       </c>
       <c r="L16">
-        <v>31</v>
-      </c>
-      <c r="M16" s="3">
-        <v>3.1359999999999998E-4</v>
+        <v>1.9483098190315E-3</v>
+      </c>
+      <c r="M16">
+        <v>33</v>
       </c>
       <c r="N16" s="3">
-        <v>5.4469999999999996E-4</v>
+        <v>3.857E-4</v>
+      </c>
+      <c r="O16">
+        <v>160</v>
+      </c>
+      <c r="P16">
+        <v>853.05</v>
+      </c>
+      <c r="Q16">
+        <v>544</v>
+      </c>
+      <c r="R16">
+        <v>2243.4</v>
+      </c>
+      <c r="S16">
+        <v>719.90007867095005</v>
+      </c>
+      <c r="T16">
+        <v>406.75</v>
+      </c>
+      <c r="U16">
+        <v>4376.5</v>
+      </c>
+      <c r="V16">
+        <v>52264.554355412598</v>
+      </c>
+      <c r="W16">
+        <v>4.4271252331900204</v>
+      </c>
+      <c r="X16">
+        <v>5.43813549640123E-2</v>
+      </c>
+      <c r="Y16">
+        <v>4.8591098621486903</v>
+      </c>
+      <c r="Z16">
+        <v>0.86875000000000002</v>
+      </c>
+      <c r="AA16">
+        <v>7</v>
+      </c>
+      <c r="AB16">
+        <v>4131</v>
+      </c>
+      <c r="AC16">
+        <v>0.94390494687535698</v>
+      </c>
+      <c r="AD16">
+        <v>1555.5</v>
+      </c>
+      <c r="AE16">
+        <v>2727</v>
+      </c>
+      <c r="AF16">
+        <v>54</v>
+      </c>
+      <c r="AG16">
+        <v>98</v>
+      </c>
+      <c r="AH16">
+        <v>0.36322241681260897</v>
+      </c>
+      <c r="AI16">
+        <v>0.355263157894737</v>
+      </c>
+      <c r="AJ16">
+        <v>10282.176804869199</v>
+      </c>
+      <c r="AK16">
+        <v>1556.0907290004</v>
+      </c>
+      <c r="AL16">
+        <v>42563.944221689097</v>
       </c>
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>9536</v>
+        <v>9770</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
         <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H17">
-        <v>2.0164610000000001</v>
+        <v>4.5517370000000001</v>
       </c>
       <c r="I17">
-        <v>1155705</v>
+        <v>4700982</v>
       </c>
       <c r="J17">
-        <v>273000000</v>
+        <v>668000000</v>
       </c>
       <c r="K17" s="5">
-        <v>4.2333516483516482E-3</v>
-      </c>
-      <c r="L17">
-        <v>44</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3.2939999999999998E-4</v>
+        <v>7.0373982035928147E-3</v>
+      </c>
+      <c r="M17">
+        <v>38</v>
       </c>
       <c r="N17" s="3">
-        <v>4.8930000000000002E-4</v>
-      </c>
-      <c r="O17">
-        <v>18</v>
-      </c>
-      <c r="P17">
-        <v>515.11111111111097</v>
-      </c>
-      <c r="Q17">
-        <v>406.5</v>
-      </c>
-      <c r="R17">
-        <v>671.7</v>
-      </c>
-      <c r="S17">
-        <v>331.00628906214598</v>
-      </c>
-      <c r="T17">
-        <v>284.75</v>
-      </c>
-      <c r="U17">
-        <v>203</v>
-      </c>
-      <c r="V17">
-        <v>24510.027842238898</v>
-      </c>
-      <c r="W17">
-        <v>2.72269647066094</v>
-      </c>
-      <c r="X17">
-        <v>0.14285714285714299</v>
-      </c>
-      <c r="Y17">
-        <v>2.8133554045006202</v>
-      </c>
-      <c r="Z17">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="AA17">
-        <v>6</v>
-      </c>
-      <c r="AB17">
-        <v>120.5</v>
-      </c>
-      <c r="AC17">
-        <v>0.59359605911330005</v>
-      </c>
-      <c r="AD17">
-        <v>71.5</v>
-      </c>
-      <c r="AE17">
-        <v>126</v>
-      </c>
-      <c r="AF17">
-        <v>8</v>
-      </c>
-      <c r="AG17">
-        <v>9</v>
-      </c>
-      <c r="AH17">
-        <v>0.36202531645569602</v>
-      </c>
-      <c r="AI17">
-        <v>0.47058823529411797</v>
-      </c>
-      <c r="AJ17">
-        <v>1256.0217837817199</v>
-      </c>
-      <c r="AK17">
-        <v>1433.09616381049</v>
-      </c>
-      <c r="AL17">
-        <v>16162.1400696405</v>
+        <v>3.8559999999999999E-4</v>
       </c>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>9516</v>
+        <v>9785</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H18">
-        <v>1.710267</v>
+        <v>4.5517370000000001</v>
       </c>
       <c r="I18">
-        <v>530001</v>
+        <v>4654231</v>
       </c>
       <c r="J18">
-        <v>110000000</v>
+        <v>650000000</v>
       </c>
       <c r="K18" s="5">
-        <v>4.8181909090909093E-3</v>
+        <v>7.1603553846153849E-3</v>
       </c>
       <c r="L18">
-        <v>57</v>
-      </c>
-      <c r="M18" s="3">
-        <v>2.7490000000000001E-4</v>
+        <v>2.3176323455254598E-3</v>
+      </c>
+      <c r="M18">
+        <v>38</v>
       </c>
       <c r="N18" s="3">
-        <v>3.836E-4</v>
+        <v>3.6870000000000002E-4</v>
       </c>
       <c r="O18">
-        <v>50</v>
+        <v>273</v>
       </c>
       <c r="P18">
-        <v>590.98</v>
+        <v>573.48351648351604</v>
       </c>
       <c r="Q18">
-        <v>423.5</v>
+        <v>449</v>
       </c>
       <c r="R18">
-        <v>925.5</v>
+        <v>796.8</v>
       </c>
       <c r="S18">
-        <v>404.12624265197098</v>
+        <v>438.18480092771301</v>
       </c>
       <c r="T18">
-        <v>395.75</v>
+        <v>228</v>
       </c>
       <c r="U18">
-        <v>1015.5</v>
+        <v>4849.5</v>
       </c>
       <c r="V18">
-        <v>32460.059499323001</v>
+        <v>45008.789331490698</v>
       </c>
       <c r="W18">
-        <v>2.7426692229538898</v>
+        <v>4.7762124998591098</v>
       </c>
       <c r="X18">
-        <v>0.43623830625307702</v>
+        <v>0.13640581503247801</v>
       </c>
       <c r="Y18">
-        <v>3.8842971182057502</v>
+        <v>5.3336622087019396</v>
       </c>
       <c r="Z18">
-        <v>0.68</v>
+        <v>0.86813186813186805</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>883</v>
+        <v>4478.5</v>
       </c>
       <c r="AC18">
-        <v>0.869522402757262</v>
+        <v>0.92349726775956298</v>
       </c>
       <c r="AD18">
-        <v>105</v>
+        <v>1660.5</v>
       </c>
       <c r="AE18">
-        <v>851</v>
+        <v>3130.5</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="AG18">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="AH18">
-        <v>0.109832635983264</v>
+        <v>0.34658735128365697</v>
       </c>
       <c r="AI18">
-        <v>0.232558139534884</v>
+        <v>0.35849056603773599</v>
       </c>
       <c r="AJ18">
-        <v>5210.4106937524002</v>
+        <v>15727.309826930201</v>
       </c>
       <c r="AK18">
-        <v>959.61725358719002</v>
+        <v>1735.83405556453</v>
       </c>
       <c r="AL18">
-        <v>19489.826420355799</v>
+        <v>30834.898360660001</v>
       </c>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>9519</v>
+        <v>10304</v>
       </c>
       <c r="B19" t="s">
         <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19">
-        <v>1.710267</v>
+        <v>60</v>
       </c>
       <c r="I19">
-        <v>644049</v>
-      </c>
-      <c r="K19" s="5"/>
+        <v>5778</v>
+      </c>
+      <c r="J19">
+        <v>45900000</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1.2588235294117646E-4</v>
+      </c>
+      <c r="L19">
+        <v>2.4220561218722399E-3</v>
+      </c>
+      <c r="M19">
+        <v>39</v>
+      </c>
+      <c r="N19" s="3">
+        <v>2.6259999999999999E-4</v>
+      </c>
+      <c r="O19">
+        <v>137</v>
+      </c>
+      <c r="P19">
+        <v>859.82481751824798</v>
+      </c>
+      <c r="Q19">
+        <v>552</v>
+      </c>
+      <c r="R19">
+        <v>2167</v>
+      </c>
+      <c r="S19">
+        <v>658.99631680005098</v>
+      </c>
+      <c r="T19">
+        <v>517</v>
+      </c>
+      <c r="U19">
+        <v>2113.5</v>
+      </c>
+      <c r="V19">
+        <v>18163.616750926602</v>
+      </c>
+      <c r="W19">
+        <v>4.3584966072445601</v>
+      </c>
+      <c r="X19">
+        <v>0.14880529926661901</v>
+      </c>
+      <c r="Y19">
+        <v>4.8149722268867903</v>
+      </c>
+      <c r="Z19">
+        <v>0.75912408759124095</v>
+      </c>
+      <c r="AA19">
+        <v>8</v>
+      </c>
+      <c r="AB19">
+        <v>1803.5</v>
+      </c>
+      <c r="AC19">
+        <v>0.85332387035722701</v>
+      </c>
+      <c r="AD19">
+        <v>575</v>
+      </c>
+      <c r="AE19">
+        <v>1474.5</v>
+      </c>
+      <c r="AF19">
+        <v>38</v>
+      </c>
+      <c r="AG19">
+        <v>90</v>
+      </c>
+      <c r="AH19">
+        <v>0.28055623322761603</v>
+      </c>
+      <c r="AI19">
+        <v>0.296875</v>
+      </c>
+      <c r="AJ19">
+        <v>21000.081659621799</v>
+      </c>
+      <c r="AK19">
+        <v>652.37841557263403</v>
+      </c>
+      <c r="AL19">
+        <v>10064.2465789253</v>
+      </c>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>9534</v>
+        <v>9517</v>
       </c>
       <c r="B20" t="s">
         <v>61</v>
@@ -2743,245 +3225,425 @@
         <v>62</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H20">
-        <v>3.1063329999999998</v>
+        <v>1.6794659999999999</v>
       </c>
       <c r="I20">
-        <v>358915</v>
-      </c>
-      <c r="K20" s="5"/>
+        <v>2520099</v>
+      </c>
+      <c r="J20">
+        <v>248000000</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1.0161689516129032E-2</v>
+      </c>
+      <c r="L20">
+        <v>2.4364572879746801E-3</v>
+      </c>
+      <c r="M20">
+        <v>40</v>
+      </c>
+      <c r="N20" s="3">
+        <v>3.8949999999999998E-4</v>
+      </c>
+      <c r="O20">
+        <v>91</v>
+      </c>
+      <c r="P20">
+        <v>679.29670329670296</v>
+      </c>
+      <c r="Q20">
+        <v>599</v>
+      </c>
+      <c r="R20">
+        <v>984</v>
+      </c>
+      <c r="S20">
+        <v>319.63143686667502</v>
+      </c>
+      <c r="T20">
+        <v>283</v>
+      </c>
+      <c r="U20">
+        <v>1255.5</v>
+      </c>
+      <c r="V20">
+        <v>11362.0623348671</v>
+      </c>
+      <c r="W20">
+        <v>4.2310986372953199</v>
+      </c>
+      <c r="X20">
+        <v>5.6551174830744698E-2</v>
+      </c>
+      <c r="Y20">
+        <v>4.4499234906434504</v>
+      </c>
+      <c r="Z20">
+        <v>0.75824175824175799</v>
+      </c>
+      <c r="AA20">
+        <v>8</v>
+      </c>
+      <c r="AB20">
+        <v>1002.5</v>
+      </c>
+      <c r="AC20">
+        <v>0.79848665870171198</v>
+      </c>
+      <c r="AD20">
+        <v>311</v>
+      </c>
+      <c r="AE20">
+        <v>824</v>
+      </c>
+      <c r="AF20">
+        <v>26</v>
+      </c>
+      <c r="AG20">
+        <v>51</v>
+      </c>
+      <c r="AH20">
+        <v>0.274008810572687</v>
+      </c>
+      <c r="AI20">
+        <v>0.337662337662338</v>
+      </c>
+      <c r="AJ20">
+        <v>23769.530440550501</v>
+      </c>
+      <c r="AK20">
+        <v>382.84306973416398</v>
+      </c>
+      <c r="AL20">
+        <v>5281.9722423213598</v>
+      </c>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>9537</v>
+        <v>9783</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H21">
-        <v>3.1063329999999998</v>
+        <v>3.7346490000000001</v>
       </c>
       <c r="I21">
-        <v>530001</v>
+        <v>1459932</v>
       </c>
       <c r="J21">
-        <v>315000000</v>
+        <v>12100000</v>
       </c>
       <c r="K21" s="5">
-        <v>1.6825428571428571E-3</v>
+        <v>0.12065553719008265</v>
       </c>
       <c r="L21">
-        <v>33</v>
-      </c>
-      <c r="M21" s="3">
-        <v>2.5070000000000002E-4</v>
+        <v>2.49972517699441E-3</v>
+      </c>
+      <c r="M21">
+        <v>40</v>
       </c>
       <c r="N21" s="3">
-        <v>3.703E-4</v>
+        <v>4.1889999999999999E-4</v>
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>9499</v>
+        <v>10305</v>
       </c>
       <c r="B22" t="s">
         <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22">
-        <v>1.6794659999999999</v>
+        <v>58</v>
       </c>
       <c r="I22">
-        <v>2073838</v>
-      </c>
-      <c r="K22" s="5"/>
+        <v>2181</v>
+      </c>
+      <c r="J22">
+        <v>33500000</v>
+      </c>
+      <c r="K22" s="5">
+        <v>6.5104477611940305E-5</v>
+      </c>
+      <c r="L22">
+        <v>2.70138525669708E-3</v>
+      </c>
+      <c r="M22">
+        <v>42</v>
+      </c>
+      <c r="N22" s="3">
+        <v>3.8230000000000002E-4</v>
+      </c>
+      <c r="O22">
+        <v>155</v>
+      </c>
+      <c r="P22">
+        <v>883.89032258064503</v>
+      </c>
+      <c r="Q22">
+        <v>523</v>
+      </c>
+      <c r="R22">
+        <v>2250</v>
+      </c>
+      <c r="S22">
+        <v>731.73016430054201</v>
+      </c>
+      <c r="T22">
+        <v>545</v>
+      </c>
+      <c r="U22">
+        <v>2990</v>
+      </c>
+      <c r="V22">
+        <v>39371.760892915401</v>
+      </c>
+      <c r="W22">
+        <v>4.4543989052614403</v>
+      </c>
+      <c r="X22">
+        <v>0.10083612040133801</v>
+      </c>
+      <c r="Y22">
+        <v>4.84885300162217</v>
+      </c>
+      <c r="Z22">
+        <v>0.80645161290322598</v>
+      </c>
+      <c r="AA22">
+        <v>8</v>
+      </c>
+      <c r="AB22">
+        <v>2612</v>
+      </c>
+      <c r="AC22">
+        <v>0.87357859531772597</v>
+      </c>
+      <c r="AD22">
+        <v>717</v>
+      </c>
+      <c r="AE22">
+        <v>2191.5</v>
+      </c>
+      <c r="AF22">
+        <v>49</v>
+      </c>
+      <c r="AG22">
+        <v>95</v>
+      </c>
+      <c r="AH22">
+        <v>0.246518824136153</v>
+      </c>
+      <c r="AI22">
+        <v>0.34027777777777801</v>
+      </c>
+      <c r="AJ22">
+        <v>8491.3094090885406</v>
+      </c>
+      <c r="AK22">
+        <v>1825.39573736529</v>
+      </c>
+      <c r="AL22">
+        <v>35212.472611111101</v>
+      </c>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>9517</v>
+        <v>10311</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
         <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G23" t="s">
         <v>53</v>
       </c>
       <c r="H23">
-        <v>1.6794659999999999</v>
+        <v>2.8395109999999999</v>
       </c>
       <c r="I23">
-        <v>2520099</v>
+        <v>577386</v>
       </c>
       <c r="J23">
-        <v>248000000</v>
+        <v>1010000000</v>
       </c>
       <c r="K23" s="5">
-        <v>1.0161689516129032E-2</v>
+        <v>5.7166930693069312E-4</v>
       </c>
       <c r="L23">
-        <v>40</v>
-      </c>
-      <c r="M23" s="3">
-        <v>3.4380000000000001E-4</v>
+        <v>2.55048517044451E-3</v>
+      </c>
+      <c r="M23">
+        <v>42</v>
       </c>
       <c r="N23" s="3">
-        <v>3.8949999999999998E-4</v>
+        <v>4.0319999999999999E-4</v>
       </c>
       <c r="O23">
-        <v>91</v>
+        <v>313</v>
       </c>
       <c r="P23">
-        <v>679.29670329670296</v>
+        <v>840.15335463258805</v>
       </c>
       <c r="Q23">
-        <v>599</v>
+        <v>503</v>
       </c>
       <c r="R23">
-        <v>984</v>
+        <v>2178.6</v>
       </c>
       <c r="S23">
-        <v>319.63143686667502</v>
+        <v>717.01695666878697</v>
       </c>
       <c r="T23">
-        <v>283</v>
+        <v>421</v>
       </c>
       <c r="U23">
-        <v>1255.5</v>
+        <v>14256.5</v>
       </c>
       <c r="V23">
-        <v>11362.0623348671</v>
+        <v>58182.304854523201</v>
       </c>
       <c r="W23">
-        <v>4.2310986372953199</v>
+        <v>4.3021209307105197</v>
       </c>
       <c r="X23">
-        <v>5.6551174830744698E-2</v>
+        <v>0.11906849507242299</v>
       </c>
       <c r="Y23">
-        <v>4.4499234906434504</v>
+        <v>5.1616528948897296</v>
       </c>
       <c r="Z23">
-        <v>0.75824175824175799</v>
+        <v>0.94888178913737997</v>
       </c>
       <c r="AA23">
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>1002.5</v>
+        <v>14098</v>
       </c>
       <c r="AC23">
-        <v>0.79848665870171198</v>
+        <v>0.98888226423035097</v>
       </c>
       <c r="AD23">
-        <v>311</v>
+        <v>5099</v>
       </c>
       <c r="AE23">
-        <v>824</v>
+        <v>9072.5</v>
       </c>
       <c r="AF23">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="AG23">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="AH23">
-        <v>0.274008810572687</v>
+        <v>0.35980665420033198</v>
       </c>
       <c r="AI23">
-        <v>0.337662337662338</v>
+        <v>0.33993399339934</v>
       </c>
       <c r="AJ23">
-        <v>23769.530440550501</v>
+        <v>32713.022680570401</v>
       </c>
       <c r="AK23">
-        <v>382.84306973416398</v>
+        <v>956.805499315426</v>
       </c>
       <c r="AL23">
-        <v>5281.9722423213598</v>
+        <v>43580.503517541103</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>9535</v>
+        <v>10318</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
         <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
         <v>53</v>
       </c>
       <c r="H24">
-        <v>1.6794659999999999</v>
+        <v>2.8395109999999999</v>
       </c>
       <c r="I24">
-        <v>1155705</v>
-      </c>
-      <c r="K24" s="5"/>
+        <v>621165</v>
+      </c>
+      <c r="J24">
+        <v>1080000000</v>
+      </c>
+      <c r="K24" s="5">
+        <v>5.7515277777777773E-4</v>
+      </c>
+      <c r="M24">
+        <v>42</v>
+      </c>
+      <c r="N24" s="3">
+        <v>4.2460000000000002E-4</v>
+      </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>9538</v>
+        <v>9536</v>
       </c>
       <c r="B25" t="s">
         <v>61</v>
@@ -2993,1001 +3655,888 @@
         <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H25">
-        <v>1.6794659999999999</v>
+        <v>2.0164610000000001</v>
       </c>
       <c r="I25">
-        <v>1075037</v>
-      </c>
-      <c r="K25" s="5"/>
+        <v>1155705</v>
+      </c>
+      <c r="J25">
+        <v>273000000</v>
+      </c>
+      <c r="K25" s="5">
+        <v>4.2333516483516482E-3</v>
+      </c>
+      <c r="L25">
+        <v>2.69761654842508E-3</v>
+      </c>
+      <c r="M25">
+        <v>44</v>
+      </c>
+      <c r="N25" s="3">
+        <v>4.8930000000000002E-4</v>
+      </c>
+      <c r="O25">
+        <v>18</v>
+      </c>
+      <c r="P25">
+        <v>515.11111111111097</v>
+      </c>
+      <c r="Q25">
+        <v>406.5</v>
+      </c>
+      <c r="R25">
+        <v>671.7</v>
+      </c>
+      <c r="S25">
+        <v>331.00628906214598</v>
+      </c>
+      <c r="T25">
+        <v>284.75</v>
+      </c>
+      <c r="U25">
+        <v>203</v>
+      </c>
+      <c r="V25">
+        <v>24510.027842238898</v>
+      </c>
+      <c r="W25">
+        <v>2.72269647066094</v>
+      </c>
+      <c r="X25">
+        <v>0.14285714285714299</v>
+      </c>
+      <c r="Y25">
+        <v>2.8133554045006202</v>
+      </c>
+      <c r="Z25">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="AA25">
+        <v>6</v>
+      </c>
+      <c r="AB25">
+        <v>120.5</v>
+      </c>
+      <c r="AC25">
+        <v>0.59359605911330005</v>
+      </c>
+      <c r="AD25">
+        <v>71.5</v>
+      </c>
+      <c r="AE25">
+        <v>126</v>
+      </c>
+      <c r="AF25">
+        <v>8</v>
+      </c>
+      <c r="AG25">
+        <v>9</v>
+      </c>
+      <c r="AH25">
+        <v>0.36202531645569602</v>
+      </c>
+      <c r="AI25">
+        <v>0.47058823529411797</v>
+      </c>
+      <c r="AJ25">
+        <v>1256.0217837817199</v>
+      </c>
+      <c r="AK25">
+        <v>1433.09616381049</v>
+      </c>
+      <c r="AL25">
+        <v>16162.1400696405</v>
+      </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>10309</v>
+        <v>9773</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H26">
-        <v>3.8831820000000001</v>
+        <v>4.1547580000000002</v>
       </c>
       <c r="I26">
-        <v>17294</v>
+        <v>1645965</v>
       </c>
       <c r="J26">
-        <v>65200000</v>
+        <v>245000000</v>
       </c>
       <c r="K26" s="5">
-        <v>2.6524539877300615E-4</v>
+        <v>6.7182244897959183E-3</v>
       </c>
       <c r="L26">
-        <v>22</v>
-      </c>
-      <c r="M26" s="3">
-        <v>2.265E-4</v>
+        <v>2.9160789187518401E-3</v>
+      </c>
+      <c r="M26">
+        <v>45</v>
       </c>
       <c r="N26" s="3">
-        <v>1.4760000000000001E-4</v>
+        <v>3.1050000000000001E-4</v>
       </c>
       <c r="O26">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="P26">
-        <v>713.71980676328496</v>
+        <v>634.48780487804902</v>
       </c>
       <c r="Q26">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="R26">
-        <v>1254.5999999999999</v>
+        <v>1000.6</v>
       </c>
       <c r="S26">
-        <v>561.92540770914502</v>
+        <v>516.672730958035</v>
       </c>
       <c r="T26">
-        <v>336.5</v>
+        <v>311</v>
       </c>
       <c r="U26">
-        <v>5393.5</v>
+        <v>2219.5</v>
       </c>
       <c r="V26">
-        <v>38521.651821192201</v>
+        <v>42147.964832050202</v>
       </c>
       <c r="W26">
-        <v>4.2872996119947899</v>
+        <v>4.1266366246850099</v>
       </c>
       <c r="X26">
-        <v>0.14378418466672799</v>
+        <v>0.14214913268754201</v>
       </c>
       <c r="Y26">
-        <v>5.1124706487555196</v>
+        <v>4.7558309260586</v>
       </c>
       <c r="Z26">
-        <v>0.82608695652173902</v>
+        <v>0.75609756097560998</v>
       </c>
       <c r="AA26">
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>5096</v>
+        <v>1910.5</v>
       </c>
       <c r="AC26">
-        <v>0.944841012329656</v>
+        <v>0.860779454832169</v>
       </c>
       <c r="AD26">
-        <v>1757.5</v>
+        <v>423.5</v>
       </c>
       <c r="AE26">
-        <v>3537</v>
+        <v>1763.5</v>
       </c>
       <c r="AF26">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="AG26">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="AH26">
-        <v>0.33194824818207602</v>
+        <v>0.19364426154549599</v>
       </c>
       <c r="AI26">
-        <v>0.335051546391753</v>
+        <v>0.29661016949152502</v>
       </c>
       <c r="AJ26">
-        <v>16626.0705569606</v>
+        <v>8465.0085073472492</v>
       </c>
       <c r="AK26">
-        <v>1245.0326088225199</v>
+        <v>1453.04047707975</v>
       </c>
       <c r="AL26">
-        <v>32440.016307653499</v>
+        <v>26219.701942101699</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>10312</v>
+        <v>9769</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G27" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H27">
-        <v>0.79092459999999998</v>
+        <v>3.085051</v>
       </c>
       <c r="I27">
-        <v>832092</v>
+        <v>3589146</v>
       </c>
       <c r="J27">
-        <v>304000000</v>
+        <v>167000000</v>
       </c>
       <c r="K27" s="5">
-        <v>2.7371447368421051E-3</v>
+        <v>2.1491892215568863E-2</v>
       </c>
       <c r="L27">
-        <v>17</v>
-      </c>
-      <c r="M27" s="3">
-        <v>3.859E-4</v>
+        <v>3.0516728353694399E-3</v>
+      </c>
+      <c r="M27">
+        <v>47</v>
       </c>
       <c r="N27" s="3">
-        <v>1.4789999999999999E-4</v>
+        <v>3.2699999999999998E-4</v>
       </c>
       <c r="O27">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="P27">
-        <v>777.32500000000005</v>
+        <v>760.01960784313701</v>
       </c>
       <c r="Q27">
-        <v>510.5</v>
+        <v>541</v>
       </c>
       <c r="R27">
-        <v>2166.6</v>
+        <v>2121</v>
       </c>
       <c r="S27">
-        <v>630.27561656008004</v>
+        <v>590.22499066698504</v>
       </c>
       <c r="T27">
-        <v>332.25</v>
+        <v>359</v>
       </c>
       <c r="U27">
-        <v>2437.5</v>
+        <v>2549.5</v>
       </c>
       <c r="V27">
-        <v>21087.690188614299</v>
+        <v>51309.438057081701</v>
       </c>
       <c r="W27">
-        <v>4.5216181276756098</v>
+        <v>2.1344300805563301</v>
       </c>
       <c r="X27">
-        <v>7.5487179487179507E-2</v>
+        <v>0.43616395371641498</v>
       </c>
       <c r="Y27">
-        <v>4.7501763803877397</v>
+        <v>3.8774611479745298</v>
       </c>
       <c r="Z27">
-        <v>0.875</v>
+        <v>0.70588235294117696</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>2278</v>
+        <v>2401.5</v>
       </c>
       <c r="AC27">
-        <v>0.93456410256410305</v>
+        <v>0.94194940184349896</v>
       </c>
       <c r="AD27">
-        <v>1067</v>
+        <v>982.5</v>
       </c>
       <c r="AE27">
-        <v>1297</v>
+        <v>1530</v>
       </c>
       <c r="AF27">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="AG27">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="AH27">
-        <v>0.451353637901861</v>
+        <v>0.39104477611940303</v>
       </c>
       <c r="AI27">
-        <v>0.38255033557047002</v>
+        <v>0.32608695652173902</v>
       </c>
       <c r="AJ27">
-        <v>17236.848245240501</v>
+        <v>6735.3550491107299</v>
       </c>
       <c r="AK27">
-        <v>928.24394415713505</v>
+        <v>757.19839010912403</v>
       </c>
       <c r="AL27">
-        <v>14141.216336768901</v>
+        <v>37852.495991827702</v>
       </c>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>10314</v>
+        <v>9768</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
       </c>
       <c r="F28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H28">
-        <v>1.029485</v>
+        <v>2.5857109999999999</v>
       </c>
       <c r="I28">
-        <v>107504</v>
+        <v>234420</v>
       </c>
       <c r="J28">
-        <v>193000000</v>
+        <v>3790000</v>
       </c>
       <c r="K28" s="5">
-        <v>5.5701554404145078E-4</v>
+        <v>6.1852242744063327E-2</v>
       </c>
       <c r="L28">
-        <v>28</v>
-      </c>
-      <c r="M28" s="3">
-        <v>1.155E-4</v>
+        <v>3.6252159347954101E-3</v>
+      </c>
+      <c r="M28">
+        <v>56</v>
       </c>
       <c r="N28" s="3">
-        <v>2.1359999999999999E-4</v>
-      </c>
-      <c r="O28">
-        <v>130</v>
-      </c>
-      <c r="P28">
-        <v>815.96923076923099</v>
-      </c>
-      <c r="Q28">
-        <v>530.5</v>
-      </c>
-      <c r="R28">
-        <v>2172</v>
-      </c>
-      <c r="S28">
-        <v>697.30149784069499</v>
-      </c>
-      <c r="T28">
-        <v>431.75</v>
-      </c>
-      <c r="U28">
-        <v>7432.5</v>
-      </c>
-      <c r="V28">
-        <v>37974.828435506599</v>
-      </c>
-      <c r="W28">
-        <v>3.6964477493640602</v>
-      </c>
-      <c r="X28">
-        <v>9.2566431214261696E-2</v>
-      </c>
-      <c r="Y28">
-        <v>4.6608972119552599</v>
-      </c>
-      <c r="Z28">
-        <v>0.89230769230769202</v>
-      </c>
-      <c r="AA28">
-        <v>8</v>
-      </c>
-      <c r="AB28">
-        <v>7268.5</v>
-      </c>
-      <c r="AC28">
-        <v>0.97793474604776298</v>
-      </c>
-      <c r="AD28">
-        <v>3698</v>
-      </c>
-      <c r="AE28">
-        <v>3646</v>
-      </c>
-      <c r="AF28">
-        <v>50</v>
-      </c>
-      <c r="AG28">
-        <v>72</v>
-      </c>
-      <c r="AH28">
-        <v>0.50354030501089297</v>
-      </c>
-      <c r="AI28">
-        <v>0.409836065573771</v>
-      </c>
-      <c r="AJ28">
-        <v>25902.683211019201</v>
-      </c>
-      <c r="AK28">
-        <v>501.87850787866199</v>
-      </c>
-      <c r="AL28">
-        <v>28693.938536985799</v>
+        <v>3.3579999999999998E-4</v>
       </c>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>10317</v>
+        <v>9516</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H29">
-        <v>0.4624934</v>
+        <v>1.710267</v>
       </c>
       <c r="I29">
-        <v>18605</v>
+        <v>530001</v>
       </c>
       <c r="J29">
-        <v>47700000</v>
+        <v>110000000</v>
       </c>
       <c r="K29" s="5">
-        <v>3.9004192872117401E-4</v>
+        <v>4.8181909090909093E-3</v>
       </c>
       <c r="L29">
-        <v>29</v>
-      </c>
-      <c r="M29" s="3">
-        <v>2.6929999999999999E-4</v>
+        <v>3.7555149091845802E-3</v>
+      </c>
+      <c r="M29">
+        <v>57</v>
       </c>
       <c r="N29" s="3">
-        <v>1.9110000000000001E-4</v>
+        <v>3.836E-4</v>
       </c>
       <c r="O29">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="P29">
-        <v>821.09230769230805</v>
+        <v>590.98</v>
       </c>
       <c r="Q29">
-        <v>706</v>
+        <v>423.5</v>
       </c>
       <c r="R29">
-        <v>1392.6</v>
+        <v>925.5</v>
       </c>
       <c r="S29">
-        <v>528.52946710297397</v>
+        <v>404.12624265197098</v>
       </c>
       <c r="T29">
-        <v>484</v>
+        <v>395.75</v>
       </c>
       <c r="U29">
-        <v>560</v>
+        <v>1015.5</v>
       </c>
       <c r="V29">
-        <v>11069.884594229899</v>
+        <v>32460.059499323001</v>
       </c>
       <c r="W29">
-        <v>4.1115170819403</v>
+        <v>2.7426692229538898</v>
       </c>
       <c r="X29">
-        <v>3.5714285714285698E-2</v>
+        <v>0.43623830625307702</v>
       </c>
       <c r="Y29">
-        <v>4.1104044532285604</v>
+        <v>3.8842971182057502</v>
       </c>
       <c r="Z29">
-        <v>0.67692307692307696</v>
+        <v>0.68</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>388</v>
+        <v>883</v>
       </c>
       <c r="AC29">
-        <v>0.69285714285714295</v>
+        <v>0.869522402757262</v>
       </c>
       <c r="AD29">
-        <v>160.5</v>
+        <v>105</v>
       </c>
       <c r="AE29">
-        <v>300</v>
+        <v>851</v>
       </c>
       <c r="AF29">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AG29">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AH29">
-        <v>0.34853420195439699</v>
+        <v>0.109832635983264</v>
       </c>
       <c r="AI29">
-        <v>0.35849056603773599</v>
+        <v>0.232558139534884</v>
       </c>
       <c r="AJ29">
-        <v>6354.2388740367996</v>
+        <v>5210.4106937524002</v>
       </c>
       <c r="AK29">
-        <v>1022.9391952132599</v>
+        <v>959.61725358719002</v>
       </c>
       <c r="AL29">
-        <v>8813.0146049142204</v>
+        <v>19489.826420355799</v>
       </c>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>10310</v>
+        <v>9786</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
       </c>
       <c r="F30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H30">
-        <v>3.7922910000000001</v>
+        <v>3.2389399999999999</v>
       </c>
       <c r="I30">
-        <v>53298</v>
-      </c>
-      <c r="K30" s="5"/>
+        <v>2430557</v>
+      </c>
+      <c r="J30">
+        <v>422000000</v>
+      </c>
+      <c r="K30" s="5">
+        <v>5.759613744075829E-3</v>
+      </c>
+      <c r="L30">
+        <v>3.7117711471151E-3</v>
+      </c>
+      <c r="M30">
+        <v>57</v>
+      </c>
+      <c r="N30" s="3">
+        <v>5.5690000000000004E-4</v>
+      </c>
+      <c r="O30">
+        <v>115</v>
+      </c>
+      <c r="P30">
+        <v>657.573913043478</v>
+      </c>
+      <c r="Q30">
+        <v>477</v>
+      </c>
+      <c r="R30">
+        <v>1180.2</v>
+      </c>
+      <c r="S30">
+        <v>496.67634031912502</v>
+      </c>
+      <c r="T30">
+        <v>331.5</v>
+      </c>
+      <c r="U30">
+        <v>1411</v>
+      </c>
+      <c r="V30">
+        <v>11727.8002217348</v>
+      </c>
+      <c r="W30">
+        <v>4.3738540755196498</v>
+      </c>
+      <c r="X30">
+        <v>7.3352232459248795E-2</v>
+      </c>
+      <c r="Y30">
+        <v>4.6439442759047802</v>
+      </c>
+      <c r="Z30">
+        <v>0.75652173913043497</v>
+      </c>
+      <c r="AA30">
+        <v>8</v>
+      </c>
+      <c r="AB30">
+        <v>1169.5</v>
+      </c>
+      <c r="AC30">
+        <v>0.82884479092842001</v>
+      </c>
+      <c r="AD30">
+        <v>381.5</v>
+      </c>
+      <c r="AE30">
+        <v>893</v>
+      </c>
+      <c r="AF30">
+        <v>35</v>
+      </c>
+      <c r="AG30">
+        <v>63</v>
+      </c>
+      <c r="AH30">
+        <v>0.29933307179286001</v>
+      </c>
+      <c r="AI30">
+        <v>0.35714285714285698</v>
+      </c>
+      <c r="AJ30">
+        <v>17483.652362722099</v>
+      </c>
+      <c r="AK30">
+        <v>657.75730158761303</v>
+      </c>
+      <c r="AL30">
+        <v>8070.39610904454</v>
+      </c>
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>10313</v>
+        <v>9518</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H31">
-        <v>3.7922910000000001</v>
+        <v>0.62796320000000005</v>
       </c>
       <c r="I31">
-        <v>59909</v>
+        <v>530001</v>
       </c>
       <c r="J31">
-        <v>47700000</v>
+        <v>16900000</v>
       </c>
       <c r="K31" s="5">
-        <v>1.2559538784067087E-3</v>
+        <v>3.1361005917159762E-2</v>
       </c>
       <c r="L31">
+        <v>4.5504212483073302E-3</v>
+      </c>
+      <c r="M31">
+        <v>69</v>
+      </c>
+      <c r="N31" s="3">
+        <v>6.6560000000000002E-4</v>
+      </c>
+      <c r="O31">
         <v>33</v>
       </c>
-      <c r="M31" s="3">
-        <v>3.1710000000000001E-4</v>
-      </c>
-      <c r="N31" s="3">
-        <v>3.857E-4</v>
-      </c>
-      <c r="O31">
-        <v>160</v>
-      </c>
       <c r="P31">
-        <v>853.05</v>
+        <v>986.09090909090901</v>
       </c>
       <c r="Q31">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="R31">
-        <v>2243.4</v>
+        <v>2251.8000000000002</v>
       </c>
       <c r="S31">
-        <v>719.90007867095005</v>
+        <v>877.78034566016197</v>
       </c>
       <c r="T31">
-        <v>406.75</v>
+        <v>617</v>
       </c>
       <c r="U31">
-        <v>4376.5</v>
+        <v>451</v>
       </c>
       <c r="V31">
-        <v>52264.554355412598</v>
+        <v>39694.298382773202</v>
       </c>
       <c r="W31">
-        <v>4.4271252331900204</v>
+        <v>3.06689569803916</v>
       </c>
       <c r="X31">
-        <v>5.43813549640123E-2</v>
+        <v>0.23725055432372499</v>
       </c>
       <c r="Y31">
-        <v>4.8591098621486903</v>
+        <v>3.45449864143254</v>
       </c>
       <c r="Z31">
-        <v>0.86875000000000002</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>4131</v>
+        <v>332.5</v>
       </c>
       <c r="AC31">
-        <v>0.94390494687535698</v>
+        <v>0.73725055432372499</v>
       </c>
       <c r="AD31">
-        <v>1555.5</v>
+        <v>77.5</v>
       </c>
       <c r="AE31">
-        <v>2727</v>
+        <v>347.5</v>
       </c>
       <c r="AF31">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="AG31">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="AH31">
-        <v>0.36322241681260897</v>
+        <v>0.182352941176471</v>
       </c>
       <c r="AI31">
-        <v>0.355263157894737</v>
+        <v>0.27586206896551702</v>
       </c>
       <c r="AJ31">
-        <v>10282.176804869199</v>
+        <v>2381.8632692490401</v>
       </c>
       <c r="AK31">
-        <v>1556.0907290004</v>
+        <v>1385.4699564851301</v>
       </c>
       <c r="AL31">
-        <v>42563.944221689097</v>
+        <v>18934.756071963398</v>
       </c>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>10220</v>
+        <v>8235</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
         <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H32">
-        <v>1.608193</v>
+        <v>60</v>
       </c>
       <c r="I32">
-        <v>8532</v>
-      </c>
-      <c r="J32">
-        <v>22900000</v>
-      </c>
-      <c r="K32" s="5">
-        <v>3.7257641921397382E-4</v>
-      </c>
-      <c r="L32">
-        <v>20</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1.85E-4</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1.771E-4</v>
-      </c>
-      <c r="O32">
-        <v>102</v>
-      </c>
-      <c r="P32">
-        <v>901.65686274509801</v>
-      </c>
-      <c r="Q32">
-        <v>619</v>
-      </c>
-      <c r="R32">
-        <v>2179.9</v>
-      </c>
-      <c r="S32">
-        <v>728.66489187788295</v>
-      </c>
-      <c r="T32">
-        <v>521.25</v>
-      </c>
-      <c r="U32">
-        <v>9271.5</v>
-      </c>
-      <c r="V32">
-        <v>37168.362349890303</v>
-      </c>
-      <c r="W32">
-        <v>2.1924551044871698</v>
-      </c>
-      <c r="X32">
-        <v>0.48028905786550202</v>
-      </c>
-      <c r="Y32">
-        <v>4.3972551067602801</v>
-      </c>
-      <c r="Z32">
-        <v>0.78431372549019596</v>
-      </c>
-      <c r="AA32">
-        <v>8</v>
-      </c>
-      <c r="AB32">
-        <v>9082</v>
-      </c>
-      <c r="AC32">
-        <v>0.97956102033112202</v>
-      </c>
-      <c r="AD32">
-        <v>864</v>
-      </c>
-      <c r="AE32">
-        <v>8305.5</v>
-      </c>
-      <c r="AF32">
-        <v>31</v>
-      </c>
-      <c r="AG32">
-        <v>59</v>
-      </c>
-      <c r="AH32">
-        <v>9.4225421233436898E-2</v>
-      </c>
-      <c r="AI32">
-        <v>0.344444444444444</v>
-      </c>
-      <c r="AJ32">
-        <v>22710.150591551599</v>
-      </c>
-      <c r="AK32">
-        <v>449.13836915702802</v>
-      </c>
-      <c r="AL32">
-        <v>40825.3567611705</v>
-      </c>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+        <v>145993</v>
+      </c>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>10315</v>
+        <v>8236</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
         <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
-      </c>
-      <c r="G33" t="s">
-        <v>58</v>
-      </c>
-      <c r="H33">
-        <v>1.608193</v>
+        <v>117</v>
       </c>
       <c r="I33">
-        <v>3220</v>
+        <v>34616</v>
       </c>
       <c r="K33" s="5"/>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>10221</v>
+        <v>8237</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
         <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>116</v>
-      </c>
-      <c r="G34" t="s">
-        <v>53</v>
-      </c>
-      <c r="H34">
-        <v>2.8395109999999999</v>
+        <v>117</v>
       </c>
       <c r="I34">
-        <v>192909</v>
+        <v>18706</v>
       </c>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>10311</v>
+        <v>8238</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
         <v>54</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s">
-        <v>116</v>
-      </c>
-      <c r="G35" t="s">
-        <v>53</v>
-      </c>
-      <c r="H35">
-        <v>2.8395109999999999</v>
+        <v>117</v>
       </c>
       <c r="I35">
-        <v>577386</v>
-      </c>
-      <c r="J35">
-        <v>1010000000</v>
-      </c>
-      <c r="K35" s="5">
-        <v>5.7166930693069312E-4</v>
-      </c>
-      <c r="L35">
-        <v>42</v>
-      </c>
-      <c r="M35" s="3">
-        <v>3.7219999999999999E-4</v>
-      </c>
-      <c r="N35" s="3">
-        <v>4.0319999999999999E-4</v>
-      </c>
-      <c r="O35">
-        <v>313</v>
-      </c>
-      <c r="P35">
-        <v>840.15335463258805</v>
-      </c>
-      <c r="Q35">
-        <v>503</v>
-      </c>
-      <c r="R35">
-        <v>2178.6</v>
-      </c>
-      <c r="S35">
-        <v>717.01695666878697</v>
-      </c>
-      <c r="T35">
-        <v>421</v>
-      </c>
-      <c r="U35">
-        <v>14256.5</v>
-      </c>
-      <c r="V35">
-        <v>58182.304854523201</v>
-      </c>
-      <c r="W35">
-        <v>4.3021209307105197</v>
-      </c>
-      <c r="X35">
-        <v>0.11906849507242299</v>
-      </c>
-      <c r="Y35">
-        <v>5.1616528948897296</v>
-      </c>
-      <c r="Z35">
-        <v>0.94888178913737997</v>
-      </c>
-      <c r="AA35">
-        <v>8</v>
-      </c>
-      <c r="AB35">
-        <v>14098</v>
-      </c>
-      <c r="AC35">
-        <v>0.98888226423035097</v>
-      </c>
-      <c r="AD35">
-        <v>5099</v>
-      </c>
-      <c r="AE35">
-        <v>9072.5</v>
-      </c>
-      <c r="AF35">
-        <v>103</v>
-      </c>
-      <c r="AG35">
-        <v>200</v>
-      </c>
-      <c r="AH35">
-        <v>0.35980665420033198</v>
-      </c>
-      <c r="AI35">
-        <v>0.33993399339934</v>
-      </c>
-      <c r="AJ35">
-        <v>32713.022680570401</v>
-      </c>
-      <c r="AK35">
-        <v>956.805499315426</v>
-      </c>
-      <c r="AL35">
-        <v>43580.503517541103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>10316</v>
+        <v>8244</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
         <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
-      </c>
-      <c r="H36">
-        <v>2.8395109999999999</v>
+        <v>46</v>
       </c>
       <c r="I36">
-        <v>107504</v>
+        <v>267934</v>
       </c>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>10318</v>
+        <v>8245</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
         <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
-      </c>
-      <c r="H37">
-        <v>2.8395109999999999</v>
+        <v>59</v>
       </c>
       <c r="I37">
-        <v>621165</v>
-      </c>
-      <c r="J37">
-        <v>1080000000</v>
-      </c>
-      <c r="K37" s="5">
-        <v>5.7515277777777773E-4</v>
-      </c>
-      <c r="L37">
-        <v>42</v>
-      </c>
-      <c r="M37" s="3">
-        <v>3.5359999999999998E-4</v>
-      </c>
-      <c r="N37" s="3">
-        <v>4.2460000000000002E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+        <v>91726</v>
+      </c>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>10299</v>
+        <v>8246</v>
       </c>
       <c r="B38" t="s">
         <v>61</v>
@@ -3996,111 +4545,22 @@
         <v>54</v>
       </c>
       <c r="D38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" t="s">
         <v>117</v>
       </c>
-      <c r="E38" t="s">
-        <v>44</v>
-      </c>
       <c r="F38" t="s">
-        <v>116</v>
-      </c>
-      <c r="G38" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <v>27200000</v>
-      </c>
-      <c r="K38" s="5">
-        <v>3.6764705882352938E-8</v>
-      </c>
-      <c r="L38">
-        <v>24</v>
-      </c>
-      <c r="M38" s="3">
-        <v>2.285E-4</v>
-      </c>
-      <c r="N38" s="3">
-        <v>2.0709999999999999E-4</v>
-      </c>
-      <c r="O38">
-        <v>150</v>
-      </c>
-      <c r="P38">
-        <v>813.72666666666703</v>
-      </c>
-      <c r="Q38">
-        <v>518.5</v>
-      </c>
-      <c r="R38">
-        <v>2166.4</v>
-      </c>
-      <c r="S38">
-        <v>700.55688200295401</v>
-      </c>
-      <c r="T38">
-        <v>454</v>
-      </c>
-      <c r="U38">
-        <v>3896.5</v>
-      </c>
-      <c r="V38">
-        <v>47278.002325241097</v>
-      </c>
-      <c r="W38">
-        <v>4.0397075671329299</v>
-      </c>
-      <c r="X38">
-        <v>0.114590016681637</v>
-      </c>
-      <c r="Y38">
-        <v>4.8685175370258396</v>
-      </c>
-      <c r="Z38">
-        <v>0.78666666666666696</v>
-      </c>
-      <c r="AA38">
-        <v>8</v>
-      </c>
-      <c r="AB38">
-        <v>3584</v>
-      </c>
-      <c r="AC38">
-        <v>0.91979982035159802</v>
-      </c>
-      <c r="AD38">
-        <v>1474</v>
-      </c>
-      <c r="AE38">
-        <v>2298.5</v>
-      </c>
-      <c r="AF38">
-        <v>59</v>
-      </c>
-      <c r="AG38">
-        <v>80</v>
-      </c>
-      <c r="AH38">
-        <v>0.39072233267064299</v>
-      </c>
-      <c r="AI38">
-        <v>0.42446043165467601</v>
-      </c>
-      <c r="AJ38">
-        <v>12504.7161306859</v>
-      </c>
-      <c r="AK38">
-        <v>1199.5474222074299</v>
-      </c>
-      <c r="AL38">
-        <v>31160.243537541799</v>
-      </c>
-    </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+        <v>4930</v>
+      </c>
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>10302</v>
+        <v>8278</v>
       </c>
       <c r="B39" t="s">
         <v>61</v>
@@ -4109,111 +4569,25 @@
         <v>54</v>
       </c>
       <c r="D39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" t="s">
         <v>117</v>
       </c>
-      <c r="E39" t="s">
-        <v>44</v>
-      </c>
       <c r="F39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G39" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I39">
-        <v>21534</v>
-      </c>
-      <c r="J39">
-        <v>12700000</v>
-      </c>
-      <c r="K39" s="5">
-        <v>1.6955905511811024E-3</v>
-      </c>
-      <c r="L39">
-        <v>28</v>
-      </c>
-      <c r="M39" s="3">
-        <v>1.4210000000000001E-4</v>
-      </c>
-      <c r="N39" s="3">
-        <v>2.4659999999999998E-4</v>
-      </c>
-      <c r="O39">
-        <v>30</v>
-      </c>
-      <c r="P39">
-        <v>971.2</v>
-      </c>
-      <c r="Q39">
-        <v>742</v>
-      </c>
-      <c r="R39">
-        <v>2265</v>
-      </c>
-      <c r="S39">
-        <v>728.30234343181701</v>
-      </c>
-      <c r="T39">
-        <v>566.75</v>
-      </c>
-      <c r="U39">
-        <v>261.5</v>
-      </c>
-      <c r="V39">
-        <v>4840.6612511248704</v>
-      </c>
-      <c r="W39">
-        <v>3.2475259107184198</v>
-      </c>
-      <c r="X39">
-        <v>0.151051625239006</v>
-      </c>
-      <c r="Y39">
-        <v>3.4011973816621599</v>
-      </c>
-      <c r="Z39">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="AA39">
-        <v>7</v>
-      </c>
-      <c r="AB39">
-        <v>182</v>
-      </c>
-      <c r="AC39">
-        <v>0.695984703632887</v>
-      </c>
-      <c r="AD39">
-        <v>80.5</v>
-      </c>
-      <c r="AE39">
-        <v>133</v>
-      </c>
-      <c r="AF39">
-        <v>10</v>
-      </c>
-      <c r="AG39">
-        <v>14</v>
-      </c>
-      <c r="AH39">
-        <v>0.37704918032786899</v>
-      </c>
-      <c r="AI39">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="AJ39">
-        <v>6884.5760893734596</v>
-      </c>
-      <c r="AK39">
-        <v>435.75667710762701</v>
-      </c>
-      <c r="AL39">
-        <v>3798.3457021214799</v>
-      </c>
-    </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+        <v>782639</v>
+      </c>
+      <c r="K39" s="5"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>10304</v>
+        <v>8279</v>
       </c>
       <c r="B40" t="s">
         <v>61</v>
@@ -4222,111 +4596,22 @@
         <v>54</v>
       </c>
       <c r="D40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s">
         <v>117</v>
       </c>
-      <c r="E40" t="s">
-        <v>44</v>
-      </c>
       <c r="F40" t="s">
-        <v>116</v>
-      </c>
-      <c r="G40" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="I40">
-        <v>5778</v>
-      </c>
-      <c r="J40">
-        <v>45900000</v>
-      </c>
-      <c r="K40" s="5">
-        <v>1.2588235294117646E-4</v>
-      </c>
-      <c r="L40">
-        <v>39</v>
-      </c>
-      <c r="M40" s="3">
-        <v>3.4440000000000002E-4</v>
-      </c>
-      <c r="N40" s="3">
-        <v>2.6259999999999999E-4</v>
-      </c>
-      <c r="O40">
-        <v>137</v>
-      </c>
-      <c r="P40">
-        <v>859.82481751824798</v>
-      </c>
-      <c r="Q40">
-        <v>552</v>
-      </c>
-      <c r="R40">
-        <v>2167</v>
-      </c>
-      <c r="S40">
-        <v>658.99631680005098</v>
-      </c>
-      <c r="T40">
-        <v>517</v>
-      </c>
-      <c r="U40">
-        <v>2113.5</v>
-      </c>
-      <c r="V40">
-        <v>18163.616750926602</v>
-      </c>
-      <c r="W40">
-        <v>4.3584966072445601</v>
-      </c>
-      <c r="X40">
-        <v>0.14880529926661901</v>
-      </c>
-      <c r="Y40">
-        <v>4.8149722268867903</v>
-      </c>
-      <c r="Z40">
-        <v>0.75912408759124095</v>
-      </c>
-      <c r="AA40">
-        <v>8</v>
-      </c>
-      <c r="AB40">
-        <v>1803.5</v>
-      </c>
-      <c r="AC40">
-        <v>0.85332387035722701</v>
-      </c>
-      <c r="AD40">
-        <v>575</v>
-      </c>
-      <c r="AE40">
-        <v>1474.5</v>
-      </c>
-      <c r="AF40">
-        <v>38</v>
-      </c>
-      <c r="AG40">
-        <v>90</v>
-      </c>
-      <c r="AH40">
-        <v>0.28055623322761603</v>
-      </c>
-      <c r="AI40">
-        <v>0.296875</v>
-      </c>
-      <c r="AJ40">
-        <v>21000.081659621799</v>
-      </c>
-      <c r="AK40">
-        <v>652.37841557263403</v>
-      </c>
-      <c r="AL40">
-        <v>10064.2465789253</v>
-      </c>
-    </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
+        <v>1804</v>
+      </c>
+      <c r="K40" s="5"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>10307</v>
+        <v>8280</v>
       </c>
       <c r="B41" t="s">
         <v>61</v>
@@ -4335,876 +4620,495 @@
         <v>54</v>
       </c>
       <c r="D41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" t="s">
         <v>117</v>
       </c>
-      <c r="E41" t="s">
-        <v>44</v>
-      </c>
       <c r="F41" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41">
-        <v>47900000</v>
-      </c>
-      <c r="K41" s="5">
-        <v>2.0876826722338206E-8</v>
-      </c>
-      <c r="L41">
-        <v>24</v>
-      </c>
-      <c r="M41" s="3">
-        <v>1.6430000000000001E-4</v>
-      </c>
-      <c r="N41" s="3">
-        <v>2.8640000000000002E-4</v>
-      </c>
-      <c r="O41">
-        <v>203</v>
-      </c>
-      <c r="P41">
-        <v>876.68965517241395</v>
-      </c>
-      <c r="Q41">
-        <v>604</v>
-      </c>
-      <c r="R41">
-        <v>2171.4</v>
-      </c>
-      <c r="S41">
-        <v>662.97163838907602</v>
-      </c>
-      <c r="T41">
-        <v>468.5</v>
-      </c>
-      <c r="U41">
-        <v>10231</v>
-      </c>
-      <c r="V41">
-        <v>55404.862127587898</v>
-      </c>
-      <c r="W41">
-        <v>3.8637220434180501</v>
-      </c>
-      <c r="X41">
-        <v>0.115091388916039</v>
-      </c>
-      <c r="Y41">
-        <v>5.1249997355283998</v>
-      </c>
-      <c r="Z41">
-        <v>0.79310344827586199</v>
-      </c>
-      <c r="AA41">
-        <v>8</v>
-      </c>
-      <c r="AB41">
-        <v>9821.5</v>
-      </c>
-      <c r="AC41">
-        <v>0.95997458703938998</v>
-      </c>
-      <c r="AD41">
-        <v>4159</v>
-      </c>
-      <c r="AE41">
-        <v>5989</v>
-      </c>
-      <c r="AF41">
-        <v>64</v>
-      </c>
-      <c r="AG41">
-        <v>128</v>
-      </c>
-      <c r="AH41">
-        <v>0.409834450137958</v>
-      </c>
-      <c r="AI41">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="AJ41">
-        <v>24710.039805949898</v>
-      </c>
-      <c r="AK41">
-        <v>821.528421622049</v>
-      </c>
-      <c r="AL41">
-        <v>41404.223062143799</v>
-      </c>
-    </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
+        <v>62117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>10005</v>
+        <v>8311</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
         <v>54</v>
       </c>
       <c r="D42" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" t="s">
         <v>117</v>
       </c>
-      <c r="E42" t="s">
-        <v>50</v>
-      </c>
       <c r="F42" t="s">
-        <v>116</v>
-      </c>
-      <c r="G42" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="I42">
-        <v>1794</v>
+        <v>111464</v>
       </c>
       <c r="K42" s="5"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>10300</v>
+        <v>8312</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
         <v>54</v>
       </c>
       <c r="D43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" t="s">
         <v>117</v>
       </c>
-      <c r="E43" t="s">
-        <v>50</v>
-      </c>
       <c r="F43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G43" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I43">
-        <v>3220</v>
-      </c>
-      <c r="J43">
-        <v>141000000</v>
-      </c>
-      <c r="K43" s="5">
-        <v>2.2836879432624115E-5</v>
-      </c>
-      <c r="L43">
-        <v>21</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1.972E-4</v>
-      </c>
-      <c r="N43" s="3">
-        <v>3.4499999999999998E-4</v>
-      </c>
-      <c r="O43">
-        <v>312</v>
-      </c>
-      <c r="P43">
-        <v>812.61538461538498</v>
-      </c>
-      <c r="Q43">
-        <v>499.5</v>
-      </c>
-      <c r="R43">
-        <v>2258.6</v>
-      </c>
-      <c r="S43">
-        <v>687.62624879088105</v>
-      </c>
-      <c r="T43">
-        <v>373.25</v>
-      </c>
-      <c r="U43">
-        <v>16339</v>
-      </c>
-      <c r="V43">
-        <v>59529.615620070297</v>
-      </c>
-      <c r="W43">
-        <v>4.4205838874190002</v>
-      </c>
-      <c r="X43">
-        <v>0.148540302344085</v>
-      </c>
-      <c r="Y43">
-        <v>5.3746788835116002</v>
-      </c>
-      <c r="Z43">
-        <v>0.91346153846153799</v>
-      </c>
-      <c r="AA43">
-        <v>8</v>
-      </c>
-      <c r="AB43">
-        <v>16139.5</v>
-      </c>
-      <c r="AC43">
-        <v>0.98778995042536299</v>
-      </c>
-      <c r="AD43">
-        <v>5844.5</v>
-      </c>
-      <c r="AE43">
-        <v>10335</v>
-      </c>
-      <c r="AF43">
-        <v>93</v>
-      </c>
-      <c r="AG43">
-        <v>208</v>
-      </c>
-      <c r="AH43">
-        <v>0.36122871534967099</v>
-      </c>
-      <c r="AI43">
-        <v>0.308970099667774</v>
-      </c>
-      <c r="AJ43">
-        <v>24910.7641359999</v>
-      </c>
-      <c r="AK43">
-        <v>1252.4706118874601</v>
-      </c>
-      <c r="AL43">
-        <v>65590.119639837299</v>
-      </c>
-    </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
+        <v>200015</v>
+      </c>
+      <c r="K43" s="5"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>10007</v>
+        <v>8313</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
         <v>54</v>
       </c>
       <c r="D44" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" t="s">
         <v>117</v>
       </c>
-      <c r="E44" t="s">
-        <v>50</v>
-      </c>
       <c r="F44" t="s">
-        <v>116</v>
-      </c>
-      <c r="G44" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>75483</v>
       </c>
       <c r="K44" s="5"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>10305</v>
+        <v>8321</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
         <v>54</v>
       </c>
       <c r="D45" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" t="s">
         <v>117</v>
       </c>
-      <c r="E45" t="s">
-        <v>50</v>
-      </c>
       <c r="F45" t="s">
-        <v>116</v>
-      </c>
-      <c r="G45" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="I45">
-        <v>2181</v>
-      </c>
-      <c r="J45">
-        <v>33500000</v>
-      </c>
-      <c r="K45" s="5">
-        <v>6.5104477611940305E-5</v>
-      </c>
-      <c r="L45">
-        <v>42</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2.2230000000000001E-4</v>
-      </c>
-      <c r="N45" s="3">
-        <v>3.8230000000000002E-4</v>
-      </c>
-      <c r="O45">
-        <v>155</v>
-      </c>
-      <c r="P45">
-        <v>883.89032258064503</v>
-      </c>
-      <c r="Q45">
-        <v>523</v>
-      </c>
-      <c r="R45">
-        <v>2250</v>
-      </c>
-      <c r="S45">
-        <v>731.73016430054201</v>
-      </c>
-      <c r="T45">
-        <v>545</v>
-      </c>
-      <c r="U45">
-        <v>2990</v>
-      </c>
-      <c r="V45">
-        <v>39371.760892915401</v>
-      </c>
-      <c r="W45">
-        <v>4.4543989052614403</v>
-      </c>
-      <c r="X45">
-        <v>0.10083612040133801</v>
-      </c>
-      <c r="Y45">
-        <v>4.84885300162217</v>
-      </c>
-      <c r="Z45">
-        <v>0.80645161290322598</v>
-      </c>
-      <c r="AA45">
-        <v>8</v>
-      </c>
-      <c r="AB45">
-        <v>2612</v>
-      </c>
-      <c r="AC45">
-        <v>0.87357859531772597</v>
-      </c>
-      <c r="AD45">
-        <v>717</v>
-      </c>
-      <c r="AE45">
-        <v>2191.5</v>
-      </c>
-      <c r="AF45">
-        <v>49</v>
-      </c>
-      <c r="AG45">
-        <v>95</v>
-      </c>
-      <c r="AH45">
-        <v>0.246518824136153</v>
-      </c>
-      <c r="AI45">
-        <v>0.34027777777777801</v>
-      </c>
-      <c r="AJ45">
-        <v>8491.3094090885406</v>
-      </c>
-      <c r="AK45">
-        <v>1825.39573736529</v>
-      </c>
-      <c r="AL45">
-        <v>35212.472611111101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
+        <v>75483</v>
+      </c>
+      <c r="K45" s="5"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>10008</v>
+        <v>8322</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
         <v>54</v>
       </c>
       <c r="D46" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" t="s">
         <v>117</v>
       </c>
-      <c r="E46" t="s">
-        <v>52</v>
-      </c>
       <c r="F46" t="s">
-        <v>116</v>
-      </c>
-      <c r="G46" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>1404396</v>
       </c>
       <c r="K46" s="5"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>10009</v>
+        <v>8323</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
         <v>54</v>
       </c>
       <c r="D47" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" t="s">
         <v>117</v>
       </c>
-      <c r="E47" t="s">
-        <v>52</v>
-      </c>
       <c r="F47" t="s">
-        <v>116</v>
-      </c>
-      <c r="G47" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="I47">
-        <v>3220</v>
-      </c>
-      <c r="J47">
-        <v>73200000</v>
-      </c>
-      <c r="K47" s="5">
-        <v>4.3989071038251367E-5</v>
-      </c>
-      <c r="L47">
-        <v>22</v>
-      </c>
-      <c r="M47" s="3">
-        <v>4.0860000000000001E-4</v>
-      </c>
-      <c r="N47" s="3">
-        <v>5.4600000000000004E-4</v>
-      </c>
-      <c r="O47">
-        <v>65</v>
-      </c>
-      <c r="P47">
-        <v>722.323076923077</v>
-      </c>
-      <c r="Q47">
-        <v>521</v>
-      </c>
-      <c r="R47">
-        <v>1896</v>
-      </c>
-      <c r="S47">
-        <v>591.84286099891801</v>
-      </c>
-      <c r="T47">
-        <v>354</v>
-      </c>
-      <c r="U47">
-        <v>6412.5</v>
-      </c>
-      <c r="V47">
-        <v>37484.871534727099</v>
-      </c>
-      <c r="W47">
-        <v>2.00770191706984</v>
-      </c>
-      <c r="X47">
-        <v>0.53512670565302101</v>
-      </c>
-      <c r="Y47">
-        <v>4.1104044532285604</v>
-      </c>
-      <c r="Z47">
-        <v>0.67692307692307696</v>
-      </c>
-      <c r="AA47">
-        <v>8</v>
-      </c>
-      <c r="AB47">
-        <v>6236</v>
-      </c>
-      <c r="AC47">
-        <v>0.97247563352826505</v>
-      </c>
-      <c r="AD47">
-        <v>4065</v>
-      </c>
-      <c r="AE47">
-        <v>2287.5</v>
-      </c>
-      <c r="AF47">
-        <v>18</v>
-      </c>
-      <c r="AG47">
-        <v>40</v>
-      </c>
-      <c r="AH47">
-        <v>0.63990554899645802</v>
-      </c>
-      <c r="AI47">
-        <v>0.31034482758620702</v>
-      </c>
-      <c r="AJ47">
-        <v>21308.731721640401</v>
-      </c>
-      <c r="AK47">
-        <v>305.03927145503599</v>
-      </c>
-      <c r="AL47">
-        <v>30093.297357006399</v>
-      </c>
-    </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
+        <v>233285</v>
+      </c>
+      <c r="K47" s="5"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>10010</v>
+        <v>8324</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s">
         <v>54</v>
       </c>
       <c r="D48" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" t="s">
         <v>117</v>
       </c>
-      <c r="E48" t="s">
-        <v>52</v>
-      </c>
       <c r="F48" t="s">
-        <v>116</v>
-      </c>
-      <c r="G48" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="I48">
-        <v>1477</v>
+        <v>13884</v>
       </c>
       <c r="K48" s="5"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>97680</v>
+        <v>8325</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="F49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G49" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I49">
-        <v>8627461.0170000009</v>
+        <v>243056</v>
       </c>
       <c r="K49" s="5"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>97730</v>
+        <v>8326</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E50" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G50" t="s">
         <v>46</v>
       </c>
       <c r="I50">
-        <v>11557049.5</v>
+        <v>463537</v>
       </c>
       <c r="K50" s="5"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>97830</v>
+        <v>8327</v>
       </c>
       <c r="B51" t="s">
         <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E51" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G51" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I51">
-        <v>27780424.48</v>
+        <v>2073838</v>
       </c>
       <c r="K51" s="5"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>97760</v>
+        <v>8538</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
         <v>35</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>118</v>
-      </c>
-      <c r="G52" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="I52">
-        <v>11557049.5</v>
+        <v>49824</v>
       </c>
       <c r="K52" s="5"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>97690</v>
+        <v>8539</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>35</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G53" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I53">
-        <v>20738383.890000001</v>
+        <v>83209</v>
       </c>
       <c r="K53" s="5"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>97860</v>
+        <v>8541</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
         <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E54" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I54">
-        <v>25200987.25</v>
+        <v>91726</v>
       </c>
       <c r="K54" s="5"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>97700</v>
+        <v>8542</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
         <v>35</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G55" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I55">
-        <v>17066020.550000001</v>
+        <v>200015</v>
       </c>
       <c r="K55" s="5"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>97850</v>
+        <v>8543</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C56" t="s">
         <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
-        <v>118</v>
-      </c>
-      <c r="G56" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="I56">
-        <v>20738383.890000001</v>
+        <v>1861</v>
       </c>
       <c r="K56" s="5"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>8598</v>
+        <v>8544</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
         <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>119</v>
-      </c>
-      <c r="G57" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="I57">
-        <v>164596</v>
+        <v>62117</v>
       </c>
       <c r="K57" s="5"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>8596</v>
+        <v>8545</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
         <v>35</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s">
-        <v>119</v>
-      </c>
-      <c r="G58" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="I58">
-        <v>62117</v>
+        <v>0</v>
       </c>
       <c r="K58" s="5"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>8600</v>
+        <v>8546</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C59" t="s">
         <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F59" t="s">
-        <v>119</v>
-      </c>
-      <c r="G59" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="I59">
-        <v>57739</v>
+        <v>44707</v>
       </c>
       <c r="K59" s="5"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>8595</v>
+        <v>8547</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C60" t="s">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G60" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I60">
-        <v>34616</v>
+        <v>111464</v>
       </c>
       <c r="K60" s="5"/>
     </row>
@@ -5222,10 +5126,10 @@
         <v>38</v>
       </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I61">
         <v>23442</v>
@@ -5234,7 +5138,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>8597</v>
+        <v>8595</v>
       </c>
       <c r="B62" t="s">
         <v>34</v>
@@ -5246,19 +5150,22 @@
         <v>38</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F62" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="G62" t="s">
+        <v>59</v>
       </c>
       <c r="I62">
-        <v>45340</v>
+        <v>34616</v>
       </c>
       <c r="K62" s="5"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>8599</v>
+        <v>8596</v>
       </c>
       <c r="B63" t="s">
         <v>34</v>
@@ -5270,19 +5177,22 @@
         <v>38</v>
       </c>
       <c r="E63" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F63" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="G63" t="s">
+        <v>46</v>
       </c>
       <c r="I63">
-        <v>18706</v>
+        <v>62117</v>
       </c>
       <c r="K63" s="5"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>8601</v>
+        <v>8597</v>
       </c>
       <c r="B64" t="s">
         <v>34</v>
@@ -5294,19 +5204,19 @@
         <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F64" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I64">
-        <v>19291</v>
+        <v>45340</v>
       </c>
       <c r="K64" s="5"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>8602</v>
+        <v>8598</v>
       </c>
       <c r="B65" t="s">
         <v>34</v>
@@ -5318,19 +5228,22 @@
         <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F65" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="G65" t="s">
+        <v>49</v>
       </c>
       <c r="I65">
-        <v>19291</v>
+        <v>164596</v>
       </c>
       <c r="K65" s="5"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>8603</v>
+        <v>8599</v>
       </c>
       <c r="B66" t="s">
         <v>34</v>
@@ -5342,127 +5255,118 @@
         <v>38</v>
       </c>
       <c r="E66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I66">
-        <v>25841</v>
+        <v>18706</v>
       </c>
       <c r="K66" s="5"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>8542</v>
+        <v>8600</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
         <v>35</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F67" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G67" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I67">
-        <v>200015</v>
+        <v>57739</v>
       </c>
       <c r="K67" s="5"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>8547</v>
+        <v>8601</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
         <v>35</v>
       </c>
       <c r="D68" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E68" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F68" t="s">
-        <v>119</v>
-      </c>
-      <c r="G68" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="I68">
-        <v>111464</v>
+        <v>19291</v>
       </c>
       <c r="K68" s="5"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>8541</v>
+        <v>8602</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
         <v>35</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E69" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F69" t="s">
-        <v>119</v>
-      </c>
-      <c r="G69" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="I69">
-        <v>91726</v>
+        <v>19291</v>
       </c>
       <c r="K69" s="5"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>8539</v>
+        <v>8603</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
         <v>35</v>
       </c>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F70" t="s">
-        <v>119</v>
-      </c>
-      <c r="G70" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="I70">
-        <v>83209</v>
+        <v>25841</v>
       </c>
       <c r="K70" s="5"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>8538</v>
+        <v>9499</v>
       </c>
       <c r="B71" t="s">
         <v>61</v>
@@ -5474,19 +5378,25 @@
         <v>62</v>
       </c>
       <c r="E71" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F71" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G71" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71">
+        <v>1.6794659999999999</v>
       </c>
       <c r="I71">
-        <v>49824</v>
+        <v>2073838</v>
       </c>
       <c r="K71" s="5"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>8543</v>
+        <v>9519</v>
       </c>
       <c r="B72" t="s">
         <v>61</v>
@@ -5498,19 +5408,25 @@
         <v>62</v>
       </c>
       <c r="E72" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F72" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G72" t="s">
+        <v>51</v>
+      </c>
+      <c r="H72">
+        <v>1.710267</v>
       </c>
       <c r="I72">
-        <v>1861</v>
+        <v>644049</v>
       </c>
       <c r="K72" s="5"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>8544</v>
+        <v>9534</v>
       </c>
       <c r="B73" t="s">
         <v>61</v>
@@ -5522,19 +5438,25 @@
         <v>62</v>
       </c>
       <c r="E73" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F73" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G73" t="s">
+        <v>58</v>
+      </c>
+      <c r="H73">
+        <v>3.1063329999999998</v>
       </c>
       <c r="I73">
-        <v>62117</v>
+        <v>358915</v>
       </c>
       <c r="K73" s="5"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>8545</v>
+        <v>9535</v>
       </c>
       <c r="B74" t="s">
         <v>61</v>
@@ -5546,19 +5468,25 @@
         <v>62</v>
       </c>
       <c r="E74" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F74" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G74" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74">
+        <v>1.6794659999999999</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>1155705</v>
       </c>
       <c r="K74" s="5"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>8546</v>
+        <v>9538</v>
       </c>
       <c r="B75" t="s">
         <v>61</v>
@@ -5570,223 +5498,253 @@
         <v>62</v>
       </c>
       <c r="E75" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F75" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G75" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75">
+        <v>1.6794659999999999</v>
       </c>
       <c r="I75">
-        <v>44707</v>
+        <v>1075037</v>
       </c>
       <c r="K75" s="5"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>8327</v>
+        <v>9774</v>
       </c>
       <c r="B76" t="s">
         <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E76" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G76" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="H76">
+        <v>3.085051</v>
       </c>
       <c r="I76">
-        <v>2073838</v>
+        <v>621165</v>
       </c>
       <c r="K76" s="5"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>8326</v>
+        <v>9775</v>
       </c>
       <c r="B77" t="s">
         <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E77" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F77" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G77" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="H77">
+        <v>4.5517370000000001</v>
       </c>
       <c r="I77">
-        <v>463537</v>
+        <v>6440492</v>
       </c>
       <c r="K77" s="5"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>8325</v>
+        <v>9777</v>
       </c>
       <c r="B78" t="s">
         <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D78" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E78" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F78" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G78" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="H78">
+        <v>3.2389399999999999</v>
       </c>
       <c r="I78">
-        <v>243056</v>
+        <v>882194</v>
       </c>
       <c r="K78" s="5"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>8312</v>
+        <v>9790</v>
       </c>
       <c r="B79" t="s">
         <v>34</v>
       </c>
       <c r="C79" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E79" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F79" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G79" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="H79">
+        <v>4.5517370000000001</v>
       </c>
       <c r="I79">
-        <v>200015</v>
+        <v>8627461</v>
       </c>
       <c r="K79" s="5"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>8321</v>
+        <v>10005</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C80" t="s">
         <v>54</v>
       </c>
       <c r="D80" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E80" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F80" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G80" t="s">
+        <v>51</v>
       </c>
       <c r="I80">
-        <v>75483</v>
+        <v>1794</v>
       </c>
       <c r="K80" s="5"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>8322</v>
+        <v>10007</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C81" t="s">
         <v>54</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E81" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F81" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G81" t="s">
+        <v>58</v>
       </c>
       <c r="I81">
-        <v>1404396</v>
+        <v>1</v>
       </c>
       <c r="K81" s="5"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>8323</v>
+        <v>10008</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C82" t="s">
         <v>54</v>
       </c>
       <c r="D82" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E82" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F82" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G82" t="s">
+        <v>53</v>
       </c>
       <c r="I82">
-        <v>233285</v>
+        <v>1</v>
       </c>
       <c r="K82" s="5"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>8324</v>
+        <v>10010</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C83" t="s">
         <v>54</v>
       </c>
       <c r="D83" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E83" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F83" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G83" t="s">
+        <v>53</v>
       </c>
       <c r="I83">
-        <v>13884</v>
+        <v>1477</v>
       </c>
       <c r="K83" s="5"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>8311</v>
+        <v>10221</v>
       </c>
       <c r="B84" t="s">
         <v>34</v>
@@ -5798,19 +5756,25 @@
         <v>72</v>
       </c>
       <c r="E84" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F84" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G84" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84">
+        <v>2.8395109999999999</v>
       </c>
       <c r="I84">
-        <v>111464</v>
+        <v>192909</v>
       </c>
       <c r="K84" s="5"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>8313</v>
+        <v>10310</v>
       </c>
       <c r="B85" t="s">
         <v>34</v>
@@ -5822,270 +5786,302 @@
         <v>72</v>
       </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F85" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="G85" t="s">
+        <v>51</v>
+      </c>
+      <c r="H85">
+        <v>3.7922910000000001</v>
       </c>
       <c r="I85">
-        <v>75483</v>
+        <v>53298</v>
       </c>
       <c r="K85" s="5"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>8278</v>
+        <v>10315</v>
       </c>
       <c r="B86" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
         <v>54</v>
       </c>
       <c r="D86" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="E86" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F86" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G86" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="H86">
+        <v>1.608193</v>
       </c>
       <c r="I86">
-        <v>782639</v>
+        <v>3220</v>
       </c>
       <c r="K86" s="5"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>8244</v>
+        <v>10316</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C87" t="s">
         <v>54</v>
       </c>
       <c r="D87" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="E87" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F87" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G87" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="H87">
+        <v>2.8395109999999999</v>
       </c>
       <c r="I87">
-        <v>267934</v>
+        <v>107504</v>
       </c>
       <c r="K87" s="5"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>8235</v>
+        <v>97680</v>
       </c>
       <c r="B88" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D88" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="F88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G88" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I88">
-        <v>145993</v>
+        <v>8627461.0170000009</v>
       </c>
       <c r="K88" s="5"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>8245</v>
+        <v>97690</v>
       </c>
       <c r="B89" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D89" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E89" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G89" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I89">
-        <v>91726</v>
+        <v>20738383.890000001</v>
       </c>
       <c r="K89" s="5"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>8236</v>
+        <v>97700</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E90" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F90" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G90" t="s">
+        <v>53</v>
       </c>
       <c r="I90">
-        <v>34616</v>
+        <v>17066020.550000001</v>
       </c>
       <c r="K90" s="5"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>8237</v>
+        <v>97730</v>
       </c>
       <c r="B91" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D91" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E91" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="F91" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G91" t="s">
+        <v>46</v>
       </c>
       <c r="I91">
-        <v>18706</v>
+        <v>11557049.5</v>
       </c>
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>8238</v>
+        <v>97760</v>
       </c>
       <c r="B92" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C92" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="F92" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G92" t="s">
+        <v>59</v>
       </c>
       <c r="I92">
-        <v>322</v>
+        <v>11557049.5</v>
       </c>
       <c r="K92" s="5"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>8246</v>
+        <v>97830</v>
       </c>
       <c r="B93" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E93" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="F93" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G93" t="s">
+        <v>60</v>
       </c>
       <c r="I93">
-        <v>4930</v>
+        <v>27780424.48</v>
       </c>
       <c r="K93" s="5"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>8279</v>
+        <v>97850</v>
       </c>
       <c r="B94" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D94" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F94" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G94" t="s">
+        <v>53</v>
       </c>
       <c r="I94">
-        <v>1804</v>
+        <v>20738383.890000001</v>
       </c>
       <c r="K94" s="5"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>8280</v>
+        <v>97860</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D95" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E95" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F95" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G95" t="s">
+        <v>58</v>
       </c>
       <c r="I95">
-        <v>62117</v>
-      </c>
+        <v>25200987.25</v>
+      </c>
+      <c r="K95" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AL99">
-    <sortCondition ref="F1:F99"/>
+  <autoFilter ref="A1:AL95" xr:uid="{93D3ACCA-9E1A-4A45-9BC3-5340C73D50B3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AL97">
+    <sortCondition ref="M1:M97"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
